--- a/sample_data/sample_dataset.xlsx
+++ b/sample_data/sample_dataset.xlsx
@@ -614,22 +614,22 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>36760.8725167836</v>
+        <v>57874.65726025539</v>
       </c>
       <c r="AA2" t="n">
-        <v>35126.90179692039</v>
+        <v>55877.73824880848</v>
       </c>
       <c r="AB2" t="n">
-        <v>30460.3332056721</v>
+        <v>65661.61054407513</v>
       </c>
       <c r="AC2" t="n">
-        <v>25629.77204491146</v>
+        <v>35298.84622353411</v>
       </c>
       <c r="AD2" t="n">
-        <v>29517.57505532358</v>
+        <v>38018.33237986097</v>
       </c>
       <c r="AE2" t="n">
-        <v>39692.39256470247</v>
+        <v>27616.10875216765</v>
       </c>
     </row>
     <row r="3">
@@ -673,22 +673,22 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>2647.240138324408</v>
+        <v>9355.505450167568</v>
       </c>
       <c r="AA3" t="n">
-        <v>2447.973193885427</v>
+        <v>7117.144140684102</v>
       </c>
       <c r="AB3" t="n">
-        <v>2514.415415748175</v>
+        <v>8641.705571818396</v>
       </c>
       <c r="AC3" t="n">
-        <v>7614.155717482525</v>
+        <v>7073.952352424168</v>
       </c>
       <c r="AD3" t="n">
-        <v>5983.522344755238</v>
+        <v>10730.17284599701</v>
       </c>
       <c r="AE3" t="n">
-        <v>10934.81551867164</v>
+        <v>7705.720587297561</v>
       </c>
     </row>
     <row r="4">
@@ -732,22 +732,22 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>15545.18087892651</v>
+        <v>19554.09444643176</v>
       </c>
       <c r="AA4" t="n">
-        <v>12449.58102133213</v>
+        <v>18516.48657505406</v>
       </c>
       <c r="AB4" t="n">
-        <v>15812.4893366268</v>
+        <v>17832.57874060218</v>
       </c>
       <c r="AC4" t="n">
-        <v>12947.79356925677</v>
+        <v>15999.15523088895</v>
       </c>
       <c r="AD4" t="n">
-        <v>12272.74285678413</v>
+        <v>17878.46765479082</v>
       </c>
       <c r="AE4" t="n">
-        <v>13279.98940303362</v>
+        <v>15212.30151906273</v>
       </c>
     </row>
     <row r="5">
@@ -791,22 +791,22 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>95093.02693015778</v>
+        <v>64160.88826979804</v>
       </c>
       <c r="AA5" t="n">
-        <v>89886.34502924068</v>
+        <v>92365.24449870652</v>
       </c>
       <c r="AB5" t="n">
-        <v>76033.5075382409</v>
+        <v>77844.5524691114</v>
       </c>
       <c r="AC5" t="n">
-        <v>81393.79296522288</v>
+        <v>82011.21419283435</v>
       </c>
       <c r="AD5" t="n">
-        <v>61551.86894343214</v>
+        <v>88551.81805128553</v>
       </c>
       <c r="AE5" t="n">
-        <v>112827.9464265956</v>
+        <v>59075.2878426159</v>
       </c>
     </row>
     <row r="6">
@@ -850,22 +850,22 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>18824.01916983544</v>
+        <v>17558.79478976267</v>
       </c>
       <c r="AA6" t="n">
-        <v>15994.22033963197</v>
+        <v>13846.86308557233</v>
       </c>
       <c r="AB6" t="n">
-        <v>16000.12297748715</v>
+        <v>13215.08119135287</v>
       </c>
       <c r="AC6" t="n">
-        <v>14804.08526537272</v>
+        <v>15087.46665734173</v>
       </c>
       <c r="AD6" t="n">
-        <v>11006.79911552457</v>
+        <v>16873.30533322081</v>
       </c>
       <c r="AE6" t="n">
-        <v>17909.01634400501</v>
+        <v>16913.65553890294</v>
       </c>
     </row>
     <row r="7">
@@ -909,22 +909,22 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>45576.3799731594</v>
+        <v>43837.14450343668</v>
       </c>
       <c r="AA7" t="n">
-        <v>41999.75434240959</v>
+        <v>36759.06166119351</v>
       </c>
       <c r="AB7" t="n">
-        <v>47977.91941646058</v>
+        <v>45659.7473731089</v>
       </c>
       <c r="AC7" t="n">
-        <v>43782.55692491298</v>
+        <v>58440.06537539424</v>
       </c>
       <c r="AD7" t="n">
-        <v>38492.23156264384</v>
+        <v>49784.78301986263</v>
       </c>
       <c r="AE7" t="n">
-        <v>53273.08013804412</v>
+        <v>51564.76291534743</v>
       </c>
     </row>
     <row r="8">
@@ -968,22 +968,22 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>10608.59927345343</v>
+        <v>8579.952601068821</v>
       </c>
       <c r="AA8" t="n">
-        <v>10765.04023474516</v>
+        <v>5550.831383296229</v>
       </c>
       <c r="AB8" t="n">
-        <v>7298.819997016921</v>
+        <v>10135.08416463494</v>
       </c>
       <c r="AC8" t="n">
-        <v>9502.760504621945</v>
+        <v>7887.631693531991</v>
       </c>
       <c r="AD8" t="n">
-        <v>10563.13799671722</v>
+        <v>7345.048331728664</v>
       </c>
       <c r="AE8" t="n">
-        <v>8695.714943208983</v>
+        <v>8339.153002853909</v>
       </c>
     </row>
     <row r="9">
@@ -1027,22 +1027,22 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>18185.52889070924</v>
+        <v>15315.60719450683</v>
       </c>
       <c r="AA9" t="n">
-        <v>16788.75471215997</v>
+        <v>16531.75103509369</v>
       </c>
       <c r="AB9" t="n">
-        <v>16686.85017486879</v>
+        <v>15493.38782127393</v>
       </c>
       <c r="AC9" t="n">
-        <v>18874.05952359384</v>
+        <v>24430.97730405581</v>
       </c>
       <c r="AD9" t="n">
-        <v>17816.79831791738</v>
+        <v>19923.81274453108</v>
       </c>
       <c r="AE9" t="n">
-        <v>17360.94666982636</v>
+        <v>12362.91031452133</v>
       </c>
     </row>
     <row r="10">
@@ -1086,22 +1086,22 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>3473.576014633495</v>
+        <v>8101.540592950849</v>
       </c>
       <c r="AA10" t="n">
-        <v>3957.492033438423</v>
+        <v>12247.04787245606</v>
       </c>
       <c r="AB10" t="n">
-        <v>4886.424693933522</v>
+        <v>7430.821616109391</v>
       </c>
       <c r="AC10" t="n">
-        <v>8931.90632815993</v>
+        <v>8235.120109120566</v>
       </c>
       <c r="AD10" t="n">
-        <v>10337.80155036524</v>
+        <v>6950.756971708575</v>
       </c>
       <c r="AE10" t="n">
-        <v>8254.936145174168</v>
+        <v>7335.751587092237</v>
       </c>
     </row>
     <row r="11">
@@ -1145,22 +1145,22 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>14354.32933161348</v>
+        <v>19071.94361255587</v>
       </c>
       <c r="AA11" t="n">
-        <v>16338.89827730383</v>
+        <v>16750.7709794697</v>
       </c>
       <c r="AB11" t="n">
-        <v>13182.6255742545</v>
+        <v>17064.39261028779</v>
       </c>
       <c r="AC11" t="n">
-        <v>16687.9335060987</v>
+        <v>12957.2979590359</v>
       </c>
       <c r="AD11" t="n">
-        <v>16690.82273678212</v>
+        <v>13929.67876476562</v>
       </c>
       <c r="AE11" t="n">
-        <v>16639.69714098098</v>
+        <v>18880.82648093908</v>
       </c>
     </row>
     <row r="12">
@@ -1204,22 +1204,22 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
-        <v>40873.10967196191</v>
+        <v>17361.53714321612</v>
       </c>
       <c r="AA12" t="n">
-        <v>46507.00602069891</v>
+        <v>14627.7896645602</v>
       </c>
       <c r="AB12" t="n">
-        <v>37153.37783028735</v>
+        <v>15388.62417887795</v>
       </c>
       <c r="AC12" t="n">
-        <v>55978.80061830094</v>
+        <v>51575.19271896917</v>
       </c>
       <c r="AD12" t="n">
-        <v>57393.8228874019</v>
+        <v>62059.12866052125</v>
       </c>
       <c r="AE12" t="n">
-        <v>62974.55775909065</v>
+        <v>33644.6386454114</v>
       </c>
     </row>
     <row r="13">
@@ -1263,22 +1263,22 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
-        <v>3427.065034360823</v>
+        <v>5077.256408539068</v>
       </c>
       <c r="AA13" t="n">
-        <v>4202.143456260884</v>
+        <v>4198.327909569181</v>
       </c>
       <c r="AB13" t="n">
-        <v>2961.356750095411</v>
+        <v>4314.782861272178</v>
       </c>
       <c r="AC13" t="n">
-        <v>2854.027905133558</v>
+        <v>3331.716103947446</v>
       </c>
       <c r="AD13" t="n">
-        <v>3420.510293363461</v>
+        <v>4441.345283051291</v>
       </c>
       <c r="AE13" t="n">
-        <v>4023.376319111361</v>
+        <v>3716.549878787241</v>
       </c>
     </row>
     <row r="14">
@@ -1322,22 +1322,22 @@
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
-        <v>32232.19704975818</v>
+        <v>40580.19533281571</v>
       </c>
       <c r="AA14" t="n">
-        <v>31395.05864349543</v>
+        <v>26910.71707698004</v>
       </c>
       <c r="AB14" t="n">
-        <v>34159.29930462222</v>
+        <v>33940.91931089461</v>
       </c>
       <c r="AC14" t="n">
-        <v>32201.16482946101</v>
+        <v>30383.66071354287</v>
       </c>
       <c r="AD14" t="n">
-        <v>36791.28541266386</v>
+        <v>42511.64795954915</v>
       </c>
       <c r="AE14" t="n">
-        <v>29664.52303164696</v>
+        <v>28493.27936731867</v>
       </c>
     </row>
     <row r="15">
@@ -1381,22 +1381,22 @@
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
-        <v>31516.71614221724</v>
+        <v>11556.14537579992</v>
       </c>
       <c r="AA15" t="n">
-        <v>26264.92962596278</v>
+        <v>10347.61290999309</v>
       </c>
       <c r="AB15" t="n">
-        <v>28067.65694559776</v>
+        <v>12020.38439259651</v>
       </c>
       <c r="AC15" t="n">
-        <v>20144.85284198551</v>
+        <v>29652.17024916628</v>
       </c>
       <c r="AD15" t="n">
-        <v>31164.74408031868</v>
+        <v>26822.1802312571</v>
       </c>
       <c r="AE15" t="n">
-        <v>31615.40123474905</v>
+        <v>31521.37441537937</v>
       </c>
     </row>
     <row r="16">
@@ -1440,22 +1440,22 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
-        <v>4290.905702313572</v>
+        <v>41764.71449067647</v>
       </c>
       <c r="AA16" t="n">
-        <v>4066.48402986387</v>
+        <v>32634.93283834621</v>
       </c>
       <c r="AB16" t="n">
-        <v>3256.785699039835</v>
+        <v>27527.89725378902</v>
       </c>
       <c r="AC16" t="n">
-        <v>12225.25329215205</v>
+        <v>13216.05103817553</v>
       </c>
       <c r="AD16" t="n">
-        <v>11151.76377490335</v>
+        <v>10229.31317232572</v>
       </c>
       <c r="AE16" t="n">
-        <v>13960.99510351205</v>
+        <v>10988.26266321992</v>
       </c>
     </row>
     <row r="17">
@@ -1499,22 +1499,22 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
-        <v>2104.817336663481</v>
+        <v>17607.67902212261</v>
       </c>
       <c r="AA17" t="n">
-        <v>2215.477612949848</v>
+        <v>16274.03744824531</v>
       </c>
       <c r="AB17" t="n">
-        <v>3107.083140306816</v>
+        <v>16455.7250420362</v>
       </c>
       <c r="AC17" t="n">
-        <v>5183.559180433667</v>
+        <v>4724.972361881119</v>
       </c>
       <c r="AD17" t="n">
-        <v>5641.319106089816</v>
+        <v>5003.418040942003</v>
       </c>
       <c r="AE17" t="n">
-        <v>5722.385683056876</v>
+        <v>5511.186687397794</v>
       </c>
     </row>
     <row r="18">
@@ -1558,22 +1558,22 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
-        <v>25110.80794736691</v>
+        <v>26804.57160515716</v>
       </c>
       <c r="AA18" t="n">
-        <v>16485.10389817103</v>
+        <v>26655.49036882949</v>
       </c>
       <c r="AB18" t="n">
-        <v>15854.43170001338</v>
+        <v>22937.44496755517</v>
       </c>
       <c r="AC18" t="n">
-        <v>27693.67561425876</v>
+        <v>27453.2621468558</v>
       </c>
       <c r="AD18" t="n">
-        <v>25772.35465715778</v>
+        <v>24039.03393957686</v>
       </c>
       <c r="AE18" t="n">
-        <v>26474.95163612335</v>
+        <v>25769.54302316835</v>
       </c>
     </row>
     <row r="19">
@@ -1617,22 +1617,22 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>11096.95139038602</v>
+        <v>12407.06872830928</v>
       </c>
       <c r="AA19" t="n">
-        <v>16517.03976748191</v>
+        <v>13659.68502789298</v>
       </c>
       <c r="AB19" t="n">
-        <v>13765.17832017944</v>
+        <v>10808.8838352676</v>
       </c>
       <c r="AC19" t="n">
-        <v>15500.88580283414</v>
+        <v>15430.99541033</v>
       </c>
       <c r="AD19" t="n">
-        <v>11945.07570773085</v>
+        <v>13126.06987452443</v>
       </c>
       <c r="AE19" t="n">
-        <v>12454.88346803099</v>
+        <v>17084.74376700812</v>
       </c>
     </row>
     <row r="20">
@@ -1676,22 +1676,22 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>29848.2286282934</v>
+        <v>28075.65427098744</v>
       </c>
       <c r="AA20" t="n">
-        <v>40744.47001251041</v>
+        <v>30727.86307772483</v>
       </c>
       <c r="AB20" t="n">
-        <v>35132.8525441219</v>
+        <v>21985.85386032621</v>
       </c>
       <c r="AC20" t="n">
-        <v>28655.26481946428</v>
+        <v>34479.54314514953</v>
       </c>
       <c r="AD20" t="n">
-        <v>23488.37616567656</v>
+        <v>32949.39844516871</v>
       </c>
       <c r="AE20" t="n">
-        <v>24181.129525354</v>
+        <v>26963.37977662325</v>
       </c>
     </row>
     <row r="21">
@@ -1735,22 +1735,22 @@
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>9805.421607599706</v>
+        <v>20276.9199923866</v>
       </c>
       <c r="AA21" t="n">
-        <v>9410.330411203637</v>
+        <v>20304.46929654</v>
       </c>
       <c r="AB21" t="n">
-        <v>8443.790683032488</v>
+        <v>24952.13081187668</v>
       </c>
       <c r="AC21" t="n">
-        <v>20885.24032471498</v>
+        <v>24373.80225963072</v>
       </c>
       <c r="AD21" t="n">
-        <v>18849.33466070134</v>
+        <v>21325.55892305771</v>
       </c>
       <c r="AE21" t="n">
-        <v>19764.11366233359</v>
+        <v>23819.47496671709</v>
       </c>
     </row>
     <row r="22">
@@ -1794,22 +1794,22 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>83045.42427057173</v>
+        <v>401993.9616919852</v>
       </c>
       <c r="AA22" t="n">
-        <v>81736.27503855767</v>
+        <v>396498.3140209383</v>
       </c>
       <c r="AB22" t="n">
-        <v>103239.6139574422</v>
+        <v>328769.4089293335</v>
       </c>
       <c r="AC22" t="n">
-        <v>117542.242453758</v>
+        <v>134093.5806343148</v>
       </c>
       <c r="AD22" t="n">
-        <v>110719.4410600165</v>
+        <v>115218.3222713247</v>
       </c>
       <c r="AE22" t="n">
-        <v>85516.05405741188</v>
+        <v>87467.32459934143</v>
       </c>
     </row>
     <row r="23">
@@ -1853,22 +1853,22 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>5009.090826568617</v>
+        <v>14528.95493094347</v>
       </c>
       <c r="AA23" t="n">
-        <v>4159.676395571504</v>
+        <v>22136.53997454542</v>
       </c>
       <c r="AB23" t="n">
-        <v>3892.595234448791</v>
+        <v>14872.99349584931</v>
       </c>
       <c r="AC23" t="n">
-        <v>16017.81352024552</v>
+        <v>13075.88023075346</v>
       </c>
       <c r="AD23" t="n">
-        <v>18209.44788342302</v>
+        <v>14948.26173439323</v>
       </c>
       <c r="AE23" t="n">
-        <v>17965.10715635717</v>
+        <v>20727.28872630483</v>
       </c>
     </row>
     <row r="24">
@@ -1912,22 +1912,22 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>7228.25116829061</v>
+        <v>8900.431687351916</v>
       </c>
       <c r="AA24" t="n">
-        <v>7582.27878636217</v>
+        <v>6842.990204101461</v>
       </c>
       <c r="AB24" t="n">
-        <v>6921.242610388318</v>
+        <v>7801.534053297273</v>
       </c>
       <c r="AC24" t="n">
-        <v>7913.248108506543</v>
+        <v>7546.329198107333</v>
       </c>
       <c r="AD24" t="n">
-        <v>7027.762341673704</v>
+        <v>8468.003953116957</v>
       </c>
       <c r="AE24" t="n">
-        <v>7816.445494772292</v>
+        <v>7061.594678813884</v>
       </c>
     </row>
     <row r="25">
@@ -1971,22 +1971,22 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>24323.31414487549</v>
+        <v>25608.45825108713</v>
       </c>
       <c r="AA25" t="n">
-        <v>25611.2518373913</v>
+        <v>23066.14614233133</v>
       </c>
       <c r="AB25" t="n">
-        <v>25092.80258010956</v>
+        <v>31209.52025273946</v>
       </c>
       <c r="AC25" t="n">
-        <v>30552.32549037066</v>
+        <v>23137.84451128752</v>
       </c>
       <c r="AD25" t="n">
-        <v>26456.66620998277</v>
+        <v>26363.66241935503</v>
       </c>
       <c r="AE25" t="n">
-        <v>24668.37848810955</v>
+        <v>24225.5347384787</v>
       </c>
     </row>
     <row r="26">
@@ -2030,22 +2030,22 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>11683.57054178633</v>
+        <v>32718.10089715895</v>
       </c>
       <c r="AA26" t="n">
-        <v>11607.34727240117</v>
+        <v>33535.65011198721</v>
       </c>
       <c r="AB26" t="n">
-        <v>16992.45262093986</v>
+        <v>19494.46790584377</v>
       </c>
       <c r="AC26" t="n">
-        <v>25243.67686294479</v>
+        <v>27941.84215414423</v>
       </c>
       <c r="AD26" t="n">
-        <v>29898.90807235012</v>
+        <v>24526.87375203549</v>
       </c>
       <c r="AE26" t="n">
-        <v>17617.60315285791</v>
+        <v>27355.13426541133</v>
       </c>
     </row>
     <row r="27">
@@ -2089,22 +2089,22 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>77733.77166871126</v>
+        <v>193429.0648397262</v>
       </c>
       <c r="AA27" t="n">
-        <v>93537.8781002256</v>
+        <v>167935.3206210333</v>
       </c>
       <c r="AB27" t="n">
-        <v>112960.7369349744</v>
+        <v>138073.2999898212</v>
       </c>
       <c r="AC27" t="n">
-        <v>96764.87744646586</v>
+        <v>78705.64755371852</v>
       </c>
       <c r="AD27" t="n">
-        <v>94081.45065965984</v>
+        <v>82769.35564093587</v>
       </c>
       <c r="AE27" t="n">
-        <v>71117.58797754972</v>
+        <v>67829.66556496432</v>
       </c>
     </row>
     <row r="28">
@@ -2148,22 +2148,22 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>54138.17274360357</v>
+        <v>66716.5394920776</v>
       </c>
       <c r="AA28" t="n">
-        <v>54928.4853739668</v>
+        <v>62672.90240927802</v>
       </c>
       <c r="AB28" t="n">
-        <v>48277.47439186717</v>
+        <v>44208.76181946915</v>
       </c>
       <c r="AC28" t="n">
-        <v>56202.7772105371</v>
+        <v>49522.75647201054</v>
       </c>
       <c r="AD28" t="n">
-        <v>64080.36411581527</v>
+        <v>49389.09273391873</v>
       </c>
       <c r="AE28" t="n">
-        <v>60068.28897732415</v>
+        <v>52545.08018132581</v>
       </c>
     </row>
     <row r="29">
@@ -2207,22 +2207,22 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>8043.004081657952</v>
+        <v>35118.63789971708</v>
       </c>
       <c r="AA29" t="n">
-        <v>6612.940846162098</v>
+        <v>29451.22259164795</v>
       </c>
       <c r="AB29" t="n">
-        <v>11011.58982573798</v>
+        <v>39184.94473628122</v>
       </c>
       <c r="AC29" t="n">
-        <v>27272.99470330897</v>
+        <v>41739.25330099121</v>
       </c>
       <c r="AD29" t="n">
-        <v>38117.09636575812</v>
+        <v>30222.6762180224</v>
       </c>
       <c r="AE29" t="n">
-        <v>28486.26041010426</v>
+        <v>36387.87886987352</v>
       </c>
     </row>
     <row r="30">
@@ -2266,22 +2266,22 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>272750.216408828</v>
+        <v>75169.20009773967</v>
       </c>
       <c r="AA30" t="n">
-        <v>288338.9297340444</v>
+        <v>118368.7141196111</v>
       </c>
       <c r="AB30" t="n">
-        <v>261019.1012083391</v>
+        <v>99279.15798794663</v>
       </c>
       <c r="AC30" t="n">
-        <v>110126.7231628892</v>
+        <v>92766.87658958063</v>
       </c>
       <c r="AD30" t="n">
-        <v>81888.11770152017</v>
+        <v>124119.9949107572</v>
       </c>
       <c r="AE30" t="n">
-        <v>100447.616613458</v>
+        <v>99433.36146396461</v>
       </c>
     </row>
     <row r="31">
@@ -2325,22 +2325,22 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
-        <v>3359.415097269658</v>
+        <v>6642.169823536631</v>
       </c>
       <c r="AA31" t="n">
-        <v>4329.193862895339</v>
+        <v>6842.851558090802</v>
       </c>
       <c r="AB31" t="n">
-        <v>4139.323035800094</v>
+        <v>7527.622483888052</v>
       </c>
       <c r="AC31" t="n">
-        <v>7450.39177681497</v>
+        <v>7138.84154275282</v>
       </c>
       <c r="AD31" t="n">
-        <v>8636.691645841176</v>
+        <v>6610.86671034443</v>
       </c>
       <c r="AE31" t="n">
-        <v>5445.986155997801</v>
+        <v>5286.450470367294</v>
       </c>
     </row>
     <row r="32">
@@ -2384,22 +2384,22 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>14162.42650026027</v>
+        <v>29333.73667993432</v>
       </c>
       <c r="AA32" t="n">
-        <v>11920.82938069031</v>
+        <v>36352.88901563646</v>
       </c>
       <c r="AB32" t="n">
-        <v>11455.82564790102</v>
+        <v>29474.19742921686</v>
       </c>
       <c r="AC32" t="n">
-        <v>11796.25456539274</v>
+        <v>11219.49386246127</v>
       </c>
       <c r="AD32" t="n">
-        <v>10727.88807112643</v>
+        <v>11199.94392667359</v>
       </c>
       <c r="AE32" t="n">
-        <v>14415.42783679749</v>
+        <v>11403.51674370976</v>
       </c>
     </row>
     <row r="33">
@@ -2443,22 +2443,22 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
-        <v>8283.378006366325</v>
+        <v>8068.170907588871</v>
       </c>
       <c r="AA33" t="n">
-        <v>8290.166101387782</v>
+        <v>11027.32719894974</v>
       </c>
       <c r="AB33" t="n">
-        <v>8893.560304234183</v>
+        <v>7372.363879946759</v>
       </c>
       <c r="AC33" t="n">
-        <v>7778.163535527478</v>
+        <v>8820.034422649944</v>
       </c>
       <c r="AD33" t="n">
-        <v>10200.12220887292</v>
+        <v>6366.508072341708</v>
       </c>
       <c r="AE33" t="n">
-        <v>8534.055008961577</v>
+        <v>9747.132264804115</v>
       </c>
     </row>
     <row r="34">
@@ -2502,22 +2502,22 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>11952.09103807066</v>
+        <v>58596.60273974932</v>
       </c>
       <c r="AA34" t="n">
-        <v>14601.64853506929</v>
+        <v>44244.3148206236</v>
       </c>
       <c r="AB34" t="n">
-        <v>15756.54900611185</v>
+        <v>49957.09383326807</v>
       </c>
       <c r="AC34" t="n">
-        <v>13112.34319318333</v>
+        <v>14929.47459830469</v>
       </c>
       <c r="AD34" t="n">
-        <v>15068.8984101736</v>
+        <v>13043.68117120595</v>
       </c>
       <c r="AE34" t="n">
-        <v>15579.26677403181</v>
+        <v>11254.14609988253</v>
       </c>
     </row>
     <row r="35">
@@ -2561,22 +2561,22 @@
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
-        <v>19034.07117297823</v>
+        <v>19557.77365245733</v>
       </c>
       <c r="AA35" t="n">
-        <v>17786.42890531487</v>
+        <v>15434.02442618717</v>
       </c>
       <c r="AB35" t="n">
-        <v>26127.15728341199</v>
+        <v>17930.15468399876</v>
       </c>
       <c r="AC35" t="n">
-        <v>5128.992196329726</v>
+        <v>5946.525999179801</v>
       </c>
       <c r="AD35" t="n">
-        <v>5226.470359047058</v>
+        <v>5344.658012805599</v>
       </c>
       <c r="AE35" t="n">
-        <v>7880.769427949499</v>
+        <v>4731.979772033915</v>
       </c>
     </row>
     <row r="36">
@@ -2620,22 +2620,22 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="n">
-        <v>39554.22210099483</v>
+        <v>37433.12859112242</v>
       </c>
       <c r="AA36" t="n">
-        <v>32065.95665447835</v>
+        <v>38865.65814337719</v>
       </c>
       <c r="AB36" t="n">
-        <v>47232.79705054989</v>
+        <v>45137.18873550519</v>
       </c>
       <c r="AC36" t="n">
-        <v>45095.60705982585</v>
+        <v>49510.84805370604</v>
       </c>
       <c r="AD36" t="n">
-        <v>31697.60540850179</v>
+        <v>37506.63183995093</v>
       </c>
       <c r="AE36" t="n">
-        <v>52188.474887763</v>
+        <v>47412.08758081884</v>
       </c>
     </row>
     <row r="37">
@@ -2679,22 +2679,22 @@
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="n">
-        <v>20847.017461567</v>
+        <v>15149.45289789323</v>
       </c>
       <c r="AA37" t="n">
-        <v>18077.72702407053</v>
+        <v>18875.63838935195</v>
       </c>
       <c r="AB37" t="n">
-        <v>15862.09569201091</v>
+        <v>17147.82554646546</v>
       </c>
       <c r="AC37" t="n">
-        <v>15282.03948237412</v>
+        <v>22581.5030840694</v>
       </c>
       <c r="AD37" t="n">
-        <v>17189.30430025868</v>
+        <v>21699.26009424637</v>
       </c>
       <c r="AE37" t="n">
-        <v>16844.71875599613</v>
+        <v>18366.64667562473</v>
       </c>
     </row>
     <row r="38">
@@ -2738,22 +2738,22 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="n">
-        <v>5359.898259642474</v>
+        <v>5085.308724532407</v>
       </c>
       <c r="AA38" t="n">
-        <v>4772.493115568804</v>
+        <v>4001.120975316815</v>
       </c>
       <c r="AB38" t="n">
-        <v>5852.027059117782</v>
+        <v>5275.956476494592</v>
       </c>
       <c r="AC38" t="n">
-        <v>5403.599274268448</v>
+        <v>5300.925557497829</v>
       </c>
       <c r="AD38" t="n">
-        <v>4004.94937991956</v>
+        <v>4936.703299802492</v>
       </c>
       <c r="AE38" t="n">
-        <v>4629.530220913016</v>
+        <v>5382.937149833717</v>
       </c>
     </row>
     <row r="39">
@@ -2797,22 +2797,22 @@
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>7822.428140646314</v>
+        <v>19369.04959561947</v>
       </c>
       <c r="AA39" t="n">
-        <v>10525.90531718371</v>
+        <v>25579.23957105374</v>
       </c>
       <c r="AB39" t="n">
-        <v>7556.368814401899</v>
+        <v>23804.58705634551</v>
       </c>
       <c r="AC39" t="n">
-        <v>6622.032258181504</v>
+        <v>8715.453137256203</v>
       </c>
       <c r="AD39" t="n">
-        <v>9223.55488097741</v>
+        <v>9678.745320221591</v>
       </c>
       <c r="AE39" t="n">
-        <v>7597.611245487975</v>
+        <v>10544.34672609473</v>
       </c>
     </row>
     <row r="40">
@@ -2856,22 +2856,22 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="n">
-        <v>31755.78624194203</v>
+        <v>27250.92667242494</v>
       </c>
       <c r="AA40" t="n">
-        <v>29359.98398855773</v>
+        <v>27797.41055418595</v>
       </c>
       <c r="AB40" t="n">
-        <v>28002.56298130901</v>
+        <v>33866.41030897687</v>
       </c>
       <c r="AC40" t="n">
-        <v>29228.61750277457</v>
+        <v>25358.87816235141</v>
       </c>
       <c r="AD40" t="n">
-        <v>37836.621903639</v>
+        <v>30417.38328511747</v>
       </c>
       <c r="AE40" t="n">
-        <v>32532.62089329675</v>
+        <v>32331.48377111738</v>
       </c>
     </row>
     <row r="41">
@@ -2915,22 +2915,22 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>68239.47248962641</v>
+        <v>15097.579775218</v>
       </c>
       <c r="AA41" t="n">
-        <v>65402.10409029938</v>
+        <v>17114.13841122067</v>
       </c>
       <c r="AB41" t="n">
-        <v>58361.79572055887</v>
+        <v>16261.23854904587</v>
       </c>
       <c r="AC41" t="n">
-        <v>51770.39455022687</v>
+        <v>50259.00714534245</v>
       </c>
       <c r="AD41" t="n">
-        <v>45188.13898282412</v>
+        <v>51211.05692902821</v>
       </c>
       <c r="AE41" t="n">
-        <v>50128.39774544113</v>
+        <v>56207.74116015636</v>
       </c>
     </row>
     <row r="42">
@@ -2974,22 +2974,22 @@
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
-        <v>808732.935663571</v>
+        <v>57729.06024433463</v>
       </c>
       <c r="AA42" t="n">
-        <v>501879.756403797</v>
+        <v>33896.94320328909</v>
       </c>
       <c r="AB42" t="n">
-        <v>595013.7441894634</v>
+        <v>38072.15160619743</v>
       </c>
       <c r="AC42" t="n">
-        <v>234099.2415105854</v>
+        <v>186796.3586772337</v>
       </c>
       <c r="AD42" t="n">
-        <v>169740.5719477032</v>
+        <v>160077.1914654272</v>
       </c>
       <c r="AE42" t="n">
-        <v>152885.4565415989</v>
+        <v>243614.5935281568</v>
       </c>
     </row>
     <row r="43">
@@ -3033,22 +3033,22 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>410146.47717376</v>
+        <v>1248252.492754481</v>
       </c>
       <c r="AA43" t="n">
-        <v>443277.5342558816</v>
+        <v>1012523.247568734</v>
       </c>
       <c r="AB43" t="n">
-        <v>423220.6076577396</v>
+        <v>813296.1751165004</v>
       </c>
       <c r="AC43" t="n">
-        <v>330137.6995191193</v>
+        <v>462202.2116080192</v>
       </c>
       <c r="AD43" t="n">
-        <v>364052.6349609427</v>
+        <v>406131.3480997942</v>
       </c>
       <c r="AE43" t="n">
-        <v>505821.7703006353</v>
+        <v>393089.1784533783</v>
       </c>
     </row>
     <row r="44">
@@ -3092,22 +3092,22 @@
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="n">
-        <v>9757.770141170409</v>
+        <v>23640.48546340665</v>
       </c>
       <c r="AA44" t="n">
-        <v>9993.604673448925</v>
+        <v>25885.52498560619</v>
       </c>
       <c r="AB44" t="n">
-        <v>9546.103869427459</v>
+        <v>38741.67770932349</v>
       </c>
       <c r="AC44" t="n">
-        <v>41573.22537525811</v>
+        <v>34411.66529172732</v>
       </c>
       <c r="AD44" t="n">
-        <v>30337.40515664757</v>
+        <v>43140.98204109216</v>
       </c>
       <c r="AE44" t="n">
-        <v>32770.30174153457</v>
+        <v>29576.25193289409</v>
       </c>
     </row>
     <row r="45">
@@ -3151,22 +3151,22 @@
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
-        <v>9622.870650732915</v>
+        <v>3225.761223357833</v>
       </c>
       <c r="AA45" t="n">
-        <v>7187.543899104271</v>
+        <v>2722.578832521293</v>
       </c>
       <c r="AB45" t="n">
-        <v>8612.322874020399</v>
+        <v>3682.797727156186</v>
       </c>
       <c r="AC45" t="n">
-        <v>8374.429559426433</v>
+        <v>9352.705829101704</v>
       </c>
       <c r="AD45" t="n">
-        <v>9197.031846003436</v>
+        <v>5782.088745009353</v>
       </c>
       <c r="AE45" t="n">
-        <v>11561.08786680579</v>
+        <v>8730.966384792695</v>
       </c>
     </row>
     <row r="46">
@@ -3210,22 +3210,22 @@
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="n">
-        <v>5327.357970545241</v>
+        <v>2640.592902627242</v>
       </c>
       <c r="AA46" t="n">
-        <v>6210.950830732025</v>
+        <v>2711.083377914625</v>
       </c>
       <c r="AB46" t="n">
-        <v>6445.933484654116</v>
+        <v>2241.409675525525</v>
       </c>
       <c r="AC46" t="n">
-        <v>2778.397236997102</v>
+        <v>2811.76794277209</v>
       </c>
       <c r="AD46" t="n">
-        <v>2597.157820146716</v>
+        <v>1934.727672054216</v>
       </c>
       <c r="AE46" t="n">
-        <v>2648.013734614807</v>
+        <v>2790.015341866083</v>
       </c>
     </row>
     <row r="47">
@@ -3269,22 +3269,22 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="n">
-        <v>30262.72445750016</v>
+        <v>30631.83189181891</v>
       </c>
       <c r="AA47" t="n">
-        <v>34530.1898286629</v>
+        <v>28024.30556552687</v>
       </c>
       <c r="AB47" t="n">
-        <v>21529.22131875584</v>
+        <v>21779.75508255545</v>
       </c>
       <c r="AC47" t="n">
-        <v>29303.54124634761</v>
+        <v>34466.9923332048</v>
       </c>
       <c r="AD47" t="n">
-        <v>37371.31343485439</v>
+        <v>26535.42303557765</v>
       </c>
       <c r="AE47" t="n">
-        <v>37628.20651754397</v>
+        <v>26601.00174246633</v>
       </c>
     </row>
     <row r="48">
@@ -3328,22 +3328,22 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>9732.04645671974</v>
+        <v>12450.17996660476</v>
       </c>
       <c r="AA48" t="n">
-        <v>9306.702784406922</v>
+        <v>9405.522251693634</v>
       </c>
       <c r="AB48" t="n">
-        <v>10797.22898773032</v>
+        <v>9916.091571565958</v>
       </c>
       <c r="AC48" t="n">
-        <v>10443.84331610909</v>
+        <v>10203.26226697534</v>
       </c>
       <c r="AD48" t="n">
-        <v>9088.126250675918</v>
+        <v>9791.188102839378</v>
       </c>
       <c r="AE48" t="n">
-        <v>10307.80668892058</v>
+        <v>8368.244060059233</v>
       </c>
     </row>
     <row r="49">
@@ -3387,22 +3387,22 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>15240.76418778515</v>
+        <v>10669.63353451393</v>
       </c>
       <c r="AA49" t="n">
-        <v>11280.69732174386</v>
+        <v>14196.70265333374</v>
       </c>
       <c r="AB49" t="n">
-        <v>12548.2918389454</v>
+        <v>16718.45492827719</v>
       </c>
       <c r="AC49" t="n">
-        <v>14208.41926912119</v>
+        <v>13784.33377363372</v>
       </c>
       <c r="AD49" t="n">
-        <v>16891.11781532409</v>
+        <v>16125.52023106072</v>
       </c>
       <c r="AE49" t="n">
-        <v>16799.20471381961</v>
+        <v>20560.34301695209</v>
       </c>
     </row>
     <row r="50">
@@ -3446,22 +3446,22 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>10539.63171725291</v>
+        <v>3299.508425091657</v>
       </c>
       <c r="AA50" t="n">
-        <v>11911.60932383416</v>
+        <v>3717.112826934094</v>
       </c>
       <c r="AB50" t="n">
-        <v>9619.603538595351</v>
+        <v>4721.271681834843</v>
       </c>
       <c r="AC50" t="n">
-        <v>14853.79590639595</v>
+        <v>12560.08728549522</v>
       </c>
       <c r="AD50" t="n">
-        <v>12118.82385058957</v>
+        <v>12821.34040324342</v>
       </c>
       <c r="AE50" t="n">
-        <v>10712.98186237044</v>
+        <v>12543.14677244361</v>
       </c>
     </row>
     <row r="51">
@@ -3505,22 +3505,22 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>15074.71309520784</v>
+        <v>43582.77825453575</v>
       </c>
       <c r="AA51" t="n">
-        <v>16711.38745172296</v>
+        <v>34286.29540487014</v>
       </c>
       <c r="AB51" t="n">
-        <v>18966.83917987744</v>
+        <v>43097.74887893073</v>
       </c>
       <c r="AC51" t="n">
-        <v>17867.49540547611</v>
+        <v>12327.89620121343</v>
       </c>
       <c r="AD51" t="n">
-        <v>21559.58583685919</v>
+        <v>18062.12036269331</v>
       </c>
       <c r="AE51" t="n">
-        <v>16833.8198843009</v>
+        <v>17143.36172738758</v>
       </c>
     </row>
     <row r="52">
@@ -3564,22 +3564,22 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>46865.29563511739</v>
+        <v>13722.13994888347</v>
       </c>
       <c r="AA52" t="n">
-        <v>60756.48411971984</v>
+        <v>19341.96696087662</v>
       </c>
       <c r="AB52" t="n">
-        <v>64768.67670463344</v>
+        <v>16452.74345220793</v>
       </c>
       <c r="AC52" t="n">
-        <v>75797.1079049666</v>
+        <v>67738.71057281244</v>
       </c>
       <c r="AD52" t="n">
-        <v>59808.71004077535</v>
+        <v>74521.04031081205</v>
       </c>
       <c r="AE52" t="n">
-        <v>68523.78046244386</v>
+        <v>73377.29072982217</v>
       </c>
     </row>
     <row r="53">
@@ -3623,22 +3623,22 @@
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
-        <v>21795.11084582492</v>
+        <v>32158.78441872649</v>
       </c>
       <c r="AA53" t="n">
-        <v>25458.63868716994</v>
+        <v>28465.51014342725</v>
       </c>
       <c r="AB53" t="n">
-        <v>23225.88440341263</v>
+        <v>22540.72549795175</v>
       </c>
       <c r="AC53" t="n">
-        <v>23397.71154669123</v>
+        <v>14909.98860733812</v>
       </c>
       <c r="AD53" t="n">
-        <v>25581.24492396154</v>
+        <v>30078.85998522623</v>
       </c>
       <c r="AE53" t="n">
-        <v>29891.56324415303</v>
+        <v>25353.61987571462</v>
       </c>
     </row>
     <row r="54">
@@ -3682,22 +3682,22 @@
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="n">
-        <v>17545.69448349782</v>
+        <v>19863.09278572134</v>
       </c>
       <c r="AA54" t="n">
-        <v>14552.48910619312</v>
+        <v>19912.85642482159</v>
       </c>
       <c r="AB54" t="n">
-        <v>21290.57874934984</v>
+        <v>18827.66965040396</v>
       </c>
       <c r="AC54" t="n">
-        <v>18626.25430101487</v>
+        <v>14513.66142153741</v>
       </c>
       <c r="AD54" t="n">
-        <v>18472.53532691055</v>
+        <v>19321.50179975519</v>
       </c>
       <c r="AE54" t="n">
-        <v>18909.19589977054</v>
+        <v>18095.76018720342</v>
       </c>
     </row>
     <row r="55">
@@ -3741,22 +3741,22 @@
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
-        <v>7482.838736326916</v>
+        <v>2839.896060467582</v>
       </c>
       <c r="AA55" t="n">
-        <v>6136.424338885139</v>
+        <v>2718.988324536597</v>
       </c>
       <c r="AB55" t="n">
-        <v>6393.390313846008</v>
+        <v>2391.426738665089</v>
       </c>
       <c r="AC55" t="n">
-        <v>6657.849838464232</v>
+        <v>8367.509239648401</v>
       </c>
       <c r="AD55" t="n">
-        <v>6897.661223055116</v>
+        <v>9033.949110109626</v>
       </c>
       <c r="AE55" t="n">
-        <v>6447.109997080091</v>
+        <v>8507.361937890722</v>
       </c>
     </row>
     <row r="56">
@@ -3800,22 +3800,22 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="n">
-        <v>5518.722766734621</v>
+        <v>10047.15939024304</v>
       </c>
       <c r="AA56" t="n">
-        <v>4436.5267271052</v>
+        <v>11443.18316761781</v>
       </c>
       <c r="AB56" t="n">
-        <v>3882.65894487115</v>
+        <v>9399.639243464224</v>
       </c>
       <c r="AC56" t="n">
-        <v>4418.566553670173</v>
+        <v>4433.508144637824</v>
       </c>
       <c r="AD56" t="n">
-        <v>4557.954765161492</v>
+        <v>4299.327288080452</v>
       </c>
       <c r="AE56" t="n">
-        <v>3365.319886293725</v>
+        <v>3400.013615179828</v>
       </c>
     </row>
     <row r="57">
@@ -3859,22 +3859,22 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
-        <v>36701.42483708778</v>
+        <v>43060.55615426335</v>
       </c>
       <c r="AA57" t="n">
-        <v>28746.29151941184</v>
+        <v>51717.89481447961</v>
       </c>
       <c r="AB57" t="n">
-        <v>28479.52626579525</v>
+        <v>51824.14714701657</v>
       </c>
       <c r="AC57" t="n">
-        <v>16822.30535476102</v>
+        <v>11376.75791555619</v>
       </c>
       <c r="AD57" t="n">
-        <v>14931.51623685326</v>
+        <v>12449.9220011983</v>
       </c>
       <c r="AE57" t="n">
-        <v>10933.88137924964</v>
+        <v>14279.58496669454</v>
       </c>
     </row>
     <row r="58">
@@ -3918,22 +3918,22 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>18068.10994331843</v>
+        <v>24501.46480194373</v>
       </c>
       <c r="AA58" t="n">
-        <v>14207.22330789977</v>
+        <v>20602.20367403031</v>
       </c>
       <c r="AB58" t="n">
-        <v>20727.76445640604</v>
+        <v>27282.28063608399</v>
       </c>
       <c r="AC58" t="n">
-        <v>20632.31927539488</v>
+        <v>18758.49776572133</v>
       </c>
       <c r="AD58" t="n">
-        <v>22816.76047459618</v>
+        <v>23176.40409058264</v>
       </c>
       <c r="AE58" t="n">
-        <v>16011.68636207023</v>
+        <v>27810.2704010991</v>
       </c>
     </row>
     <row r="59">
@@ -3977,22 +3977,22 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
-        <v>135955.9454120499</v>
+        <v>133634.2162033037</v>
       </c>
       <c r="AA59" t="n">
-        <v>145169.3860215692</v>
+        <v>123237.3476719385</v>
       </c>
       <c r="AB59" t="n">
-        <v>134559.2035511623</v>
+        <v>153022.0359947365</v>
       </c>
       <c r="AC59" t="n">
-        <v>125291.3443106142</v>
+        <v>158500.1885473581</v>
       </c>
       <c r="AD59" t="n">
-        <v>162506.7407885911</v>
+        <v>131205.7370388914</v>
       </c>
       <c r="AE59" t="n">
-        <v>131183.5435671849</v>
+        <v>138393.5286702366</v>
       </c>
     </row>
     <row r="60">
@@ -4036,22 +4036,22 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="n">
-        <v>23604.97528652097</v>
+        <v>25989.15605972099</v>
       </c>
       <c r="AA60" t="n">
-        <v>26137.59516751995</v>
+        <v>22409.6149462688</v>
       </c>
       <c r="AB60" t="n">
-        <v>21570.68679210106</v>
+        <v>21854.16853150407</v>
       </c>
       <c r="AC60" t="n">
-        <v>21228.11957903874</v>
+        <v>23334.07463049251</v>
       </c>
       <c r="AD60" t="n">
-        <v>31184.49333200653</v>
+        <v>25096.29484498773</v>
       </c>
       <c r="AE60" t="n">
-        <v>29703.82515897362</v>
+        <v>23714.51782188617</v>
       </c>
     </row>
     <row r="61">
@@ -4095,22 +4095,22 @@
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
-        <v>208711.0813332151</v>
+        <v>61285.03696344914</v>
       </c>
       <c r="AA61" t="n">
-        <v>195688.5298348472</v>
+        <v>50407.74487640645</v>
       </c>
       <c r="AB61" t="n">
-        <v>242802.3861922103</v>
+        <v>66902.55319030302</v>
       </c>
       <c r="AC61" t="n">
-        <v>56859.89923195692</v>
+        <v>82386.55687634811</v>
       </c>
       <c r="AD61" t="n">
-        <v>55631.10729703929</v>
+        <v>73400.24458747578</v>
       </c>
       <c r="AE61" t="n">
-        <v>58731.24476428319</v>
+        <v>54539.13077890763</v>
       </c>
     </row>
     <row r="62">
@@ -4154,22 +4154,22 @@
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="n">
-        <v>13746.00133599586</v>
+        <v>11745.23155092808</v>
       </c>
       <c r="AA62" t="n">
-        <v>10972.85604408682</v>
+        <v>11092.60149758945</v>
       </c>
       <c r="AB62" t="n">
-        <v>13496.08276427469</v>
+        <v>14715.37821299771</v>
       </c>
       <c r="AC62" t="n">
-        <v>10527.91165926485</v>
+        <v>13365.29129216488</v>
       </c>
       <c r="AD62" t="n">
-        <v>14138.57631190125</v>
+        <v>9256.428685890171</v>
       </c>
       <c r="AE62" t="n">
-        <v>9524.685564606798</v>
+        <v>12571.06980122755</v>
       </c>
     </row>
     <row r="63">
@@ -4213,22 +4213,22 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="n">
-        <v>7390.361285143239</v>
+        <v>6587.485103685338</v>
       </c>
       <c r="AA63" t="n">
-        <v>7634.459464016495</v>
+        <v>5894.273919999247</v>
       </c>
       <c r="AB63" t="n">
-        <v>5070.85284065633</v>
+        <v>7197.133330739513</v>
       </c>
       <c r="AC63" t="n">
-        <v>5873.021612988876</v>
+        <v>7159.974225195388</v>
       </c>
       <c r="AD63" t="n">
-        <v>6133.471183176128</v>
+        <v>5444.730874958945</v>
       </c>
       <c r="AE63" t="n">
-        <v>6544.905007795001</v>
+        <v>6483.150321124087</v>
       </c>
     </row>
     <row r="64">
@@ -4272,22 +4272,22 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="n">
-        <v>7974.422132754643</v>
+        <v>8200.946536734709</v>
       </c>
       <c r="AA64" t="n">
-        <v>8842.154354067847</v>
+        <v>8302.244513331207</v>
       </c>
       <c r="AB64" t="n">
-        <v>6254.737913529081</v>
+        <v>10120.64856080659</v>
       </c>
       <c r="AC64" t="n">
-        <v>8681.079312514818</v>
+        <v>10693.74636307673</v>
       </c>
       <c r="AD64" t="n">
-        <v>8420.180425258923</v>
+        <v>7022.135645867633</v>
       </c>
       <c r="AE64" t="n">
-        <v>8188.314764982849</v>
+        <v>7928.44542217194</v>
       </c>
     </row>
     <row r="65">
@@ -4331,22 +4331,22 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>12510.85148351364</v>
+        <v>11296.89304492</v>
       </c>
       <c r="AA65" t="n">
-        <v>15247.40003308621</v>
+        <v>11213.999193212</v>
       </c>
       <c r="AB65" t="n">
-        <v>10645.85657584132</v>
+        <v>11732.04900227414</v>
       </c>
       <c r="AC65" t="n">
-        <v>12998.9766631429</v>
+        <v>10877.24207902399</v>
       </c>
       <c r="AD65" t="n">
-        <v>9747.942519638134</v>
+        <v>10099.94076871939</v>
       </c>
       <c r="AE65" t="n">
-        <v>14605.79647875576</v>
+        <v>12237.01497368894</v>
       </c>
     </row>
     <row r="66">
@@ -4390,22 +4390,22 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="n">
-        <v>349888.2785381262</v>
+        <v>86716.50791604373</v>
       </c>
       <c r="AA66" t="n">
-        <v>442275.469928761</v>
+        <v>75214.342697575</v>
       </c>
       <c r="AB66" t="n">
-        <v>401721.6900711097</v>
+        <v>83402.03977453381</v>
       </c>
       <c r="AC66" t="n">
-        <v>282053.3063368155</v>
+        <v>159232.0952387261</v>
       </c>
       <c r="AD66" t="n">
-        <v>235974.7953183061</v>
+        <v>178131.7113358582</v>
       </c>
       <c r="AE66" t="n">
-        <v>148731.6635410548</v>
+        <v>142698.3680191965</v>
       </c>
     </row>
     <row r="67">
@@ -4449,22 +4449,22 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>34526.90275881685</v>
+        <v>8265.395888300212</v>
       </c>
       <c r="AA67" t="n">
-        <v>36559.58597930488</v>
+        <v>8636.762052898841</v>
       </c>
       <c r="AB67" t="n">
-        <v>33963.10994231421</v>
+        <v>10658.88678701667</v>
       </c>
       <c r="AC67" t="n">
-        <v>8871.734101137585</v>
+        <v>9529.563596729136</v>
       </c>
       <c r="AD67" t="n">
-        <v>10230.90216599948</v>
+        <v>7727.297539087454</v>
       </c>
       <c r="AE67" t="n">
-        <v>9136.308331406955</v>
+        <v>11024.91872424641</v>
       </c>
     </row>
     <row r="68">
@@ -4508,22 +4508,22 @@
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="n">
-        <v>75217.58026427949</v>
+        <v>49997.97827978085</v>
       </c>
       <c r="AA68" t="n">
-        <v>49684.58555701362</v>
+        <v>58309.30052461554</v>
       </c>
       <c r="AB68" t="n">
-        <v>50730.96919048994</v>
+        <v>53616.27370821086</v>
       </c>
       <c r="AC68" t="n">
-        <v>63182.60009227444</v>
+        <v>50672.95388553244</v>
       </c>
       <c r="AD68" t="n">
-        <v>49305.20016658968</v>
+        <v>43945.93902200131</v>
       </c>
       <c r="AE68" t="n">
-        <v>65799.47284571566</v>
+        <v>48123.9967666229</v>
       </c>
     </row>
     <row r="69">
@@ -4567,22 +4567,22 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="n">
-        <v>9232.958281098943</v>
+        <v>41463.58401902307</v>
       </c>
       <c r="AA69" t="n">
-        <v>10092.91732609508</v>
+        <v>37095.99889095819</v>
       </c>
       <c r="AB69" t="n">
-        <v>9236.393714735656</v>
+        <v>25407.78306299175</v>
       </c>
       <c r="AC69" t="n">
-        <v>9261.633296268546</v>
+        <v>7276.182152899867</v>
       </c>
       <c r="AD69" t="n">
-        <v>10679.86644932799</v>
+        <v>7847.470818484601</v>
       </c>
       <c r="AE69" t="n">
-        <v>9552.608839836288</v>
+        <v>9448.535073248451</v>
       </c>
     </row>
     <row r="70">
@@ -4626,22 +4626,22 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="n">
-        <v>33248.80719406898</v>
+        <v>50012.82635197557</v>
       </c>
       <c r="AA70" t="n">
-        <v>29453.10969232105</v>
+        <v>54591.07936333924</v>
       </c>
       <c r="AB70" t="n">
-        <v>30913.22723236801</v>
+        <v>56619.92162777908</v>
       </c>
       <c r="AC70" t="n">
-        <v>54659.91289281271</v>
+        <v>53809.11750653695</v>
       </c>
       <c r="AD70" t="n">
-        <v>40375.5911298563</v>
+        <v>80836.72242223169</v>
       </c>
       <c r="AE70" t="n">
-        <v>60844.09026032015</v>
+        <v>47217.73423593269</v>
       </c>
     </row>
     <row r="71">
@@ -4685,22 +4685,22 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>110662.70798725</v>
+        <v>13194.49054169327</v>
       </c>
       <c r="AA71" t="n">
-        <v>131698.8178948932</v>
+        <v>13533.92424151492</v>
       </c>
       <c r="AB71" t="n">
-        <v>92396.87396663461</v>
+        <v>13731.71427341301</v>
       </c>
       <c r="AC71" t="n">
-        <v>34538.85267500453</v>
+        <v>28958.58984180475</v>
       </c>
       <c r="AD71" t="n">
-        <v>23928.74121875824</v>
+        <v>42413.08738222114</v>
       </c>
       <c r="AE71" t="n">
-        <v>32929.97550960704</v>
+        <v>39507.49288272532</v>
       </c>
     </row>
     <row r="72">
@@ -4744,22 +4744,22 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>20547.17347443772</v>
+        <v>5475.779819016439</v>
       </c>
       <c r="AA72" t="n">
-        <v>17416.3319805458</v>
+        <v>5767.582167510959</v>
       </c>
       <c r="AB72" t="n">
-        <v>15796.85839376274</v>
+        <v>4384.223923738394</v>
       </c>
       <c r="AC72" t="n">
-        <v>19008.65298793686</v>
+        <v>21633.87745952533</v>
       </c>
       <c r="AD72" t="n">
-        <v>21220.81674077291</v>
+        <v>17704.95264172384</v>
       </c>
       <c r="AE72" t="n">
-        <v>19788.44841685064</v>
+        <v>22701.97822998217</v>
       </c>
     </row>
     <row r="73">
@@ -4803,22 +4803,22 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>20967.31330300516</v>
+        <v>24002.06752362491</v>
       </c>
       <c r="AA73" t="n">
-        <v>19809.68726656225</v>
+        <v>21751.40238669594</v>
       </c>
       <c r="AB73" t="n">
-        <v>17948.08844949801</v>
+        <v>27214.6297667025</v>
       </c>
       <c r="AC73" t="n">
-        <v>21499.75530109135</v>
+        <v>21256.73903194737</v>
       </c>
       <c r="AD73" t="n">
-        <v>21339.34308438316</v>
+        <v>20024.26326140225</v>
       </c>
       <c r="AE73" t="n">
-        <v>23762.85445858072</v>
+        <v>24420.44701371463</v>
       </c>
     </row>
     <row r="74">
@@ -4862,22 +4862,22 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>24953.4581949836</v>
+        <v>11463.53277582107</v>
       </c>
       <c r="AA74" t="n">
-        <v>23824.34790913621</v>
+        <v>9209.521888237239</v>
       </c>
       <c r="AB74" t="n">
-        <v>26733.32875251507</v>
+        <v>14832.28652582811</v>
       </c>
       <c r="AC74" t="n">
-        <v>10763.99804417935</v>
+        <v>10968.61116447613</v>
       </c>
       <c r="AD74" t="n">
-        <v>11881.99192848928</v>
+        <v>9631.860697665657</v>
       </c>
       <c r="AE74" t="n">
-        <v>10135.39829154171</v>
+        <v>9117.939159693229</v>
       </c>
     </row>
     <row r="75">
@@ -4921,22 +4921,22 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>30612.07573551194</v>
+        <v>41999.63849840493</v>
       </c>
       <c r="AA75" t="n">
-        <v>38742.49968996076</v>
+        <v>34059.87087427999</v>
       </c>
       <c r="AB75" t="n">
-        <v>41473.68083479546</v>
+        <v>42190.70822449935</v>
       </c>
       <c r="AC75" t="n">
-        <v>27899.26860279493</v>
+        <v>33865.25738309517</v>
       </c>
       <c r="AD75" t="n">
-        <v>28201.00193723705</v>
+        <v>25844.48832234749</v>
       </c>
       <c r="AE75" t="n">
-        <v>39252.91501371996</v>
+        <v>38965.82902287255</v>
       </c>
     </row>
     <row r="76">
@@ -4980,22 +4980,22 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>51212.05117966377</v>
+        <v>15891.43584575725</v>
       </c>
       <c r="AA76" t="n">
-        <v>60110.57850754423</v>
+        <v>14535.10288603315</v>
       </c>
       <c r="AB76" t="n">
-        <v>45002.98223091061</v>
+        <v>14520.23586201961</v>
       </c>
       <c r="AC76" t="n">
-        <v>11086.38146807561</v>
+        <v>14450.50762122576</v>
       </c>
       <c r="AD76" t="n">
-        <v>13926.25885233696</v>
+        <v>13732.00462933753</v>
       </c>
       <c r="AE76" t="n">
-        <v>11373.78093044891</v>
+        <v>14849.84613361703</v>
       </c>
     </row>
     <row r="77">
@@ -5039,22 +5039,22 @@
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>5691.127475569455</v>
+        <v>7336.867403649155</v>
       </c>
       <c r="AA77" t="n">
-        <v>6036.4306379223</v>
+        <v>5650.164949180687</v>
       </c>
       <c r="AB77" t="n">
-        <v>4443.240624613328</v>
+        <v>7918.74493442635</v>
       </c>
       <c r="AC77" t="n">
-        <v>7132.24241895912</v>
+        <v>7093.373846304143</v>
       </c>
       <c r="AD77" t="n">
-        <v>8733.492689404227</v>
+        <v>5567.583733684085</v>
       </c>
       <c r="AE77" t="n">
-        <v>6793.010073796733</v>
+        <v>5082.72873625075</v>
       </c>
     </row>
     <row r="78">
@@ -5098,22 +5098,22 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>6781.13798419961</v>
+        <v>6668.697889450287</v>
       </c>
       <c r="AA78" t="n">
-        <v>5758.005155365974</v>
+        <v>6314.090072934078</v>
       </c>
       <c r="AB78" t="n">
-        <v>4752.6778510322</v>
+        <v>6147.928057214544</v>
       </c>
       <c r="AC78" t="n">
-        <v>5887.327344781453</v>
+        <v>5282.240328665196</v>
       </c>
       <c r="AD78" t="n">
-        <v>6944.41048801001</v>
+        <v>6059.210838606974</v>
       </c>
       <c r="AE78" t="n">
-        <v>6303.583562914269</v>
+        <v>6114.497184183723</v>
       </c>
     </row>
     <row r="79">
@@ -5157,22 +5157,22 @@
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>12707.3730526545</v>
+        <v>37113.49328118296</v>
       </c>
       <c r="AA79" t="n">
-        <v>11319.20582201619</v>
+        <v>21043.86915055625</v>
       </c>
       <c r="AB79" t="n">
-        <v>9529.896157704359</v>
+        <v>26984.21944868517</v>
       </c>
       <c r="AC79" t="n">
-        <v>23936.85457831478</v>
+        <v>22389.55362030659</v>
       </c>
       <c r="AD79" t="n">
-        <v>26850.61217507146</v>
+        <v>20589.92258882358</v>
       </c>
       <c r="AE79" t="n">
-        <v>23864.42068542858</v>
+        <v>27646.87805236329</v>
       </c>
     </row>
     <row r="80">
@@ -5216,22 +5216,22 @@
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>112878.9142090393</v>
+        <v>103602.527277509</v>
       </c>
       <c r="AA80" t="n">
-        <v>102973.5081197389</v>
+        <v>130550.9918293224</v>
       </c>
       <c r="AB80" t="n">
-        <v>98265.85819641473</v>
+        <v>90678.04552426306</v>
       </c>
       <c r="AC80" t="n">
-        <v>106976.7821256921</v>
+        <v>126095.2860625316</v>
       </c>
       <c r="AD80" t="n">
-        <v>100030.7752270482</v>
+        <v>95300.9528162218</v>
       </c>
       <c r="AE80" t="n">
-        <v>106477.4457929306</v>
+        <v>116134.2986598552</v>
       </c>
     </row>
     <row r="81">
@@ -5275,22 +5275,22 @@
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>76909.5675222737</v>
+        <v>19138.61440519557</v>
       </c>
       <c r="AA81" t="n">
-        <v>92608.01026856923</v>
+        <v>31169.1502728396</v>
       </c>
       <c r="AB81" t="n">
-        <v>75513.33776803967</v>
+        <v>27434.0524047488</v>
       </c>
       <c r="AC81" t="n">
-        <v>29121.48367850448</v>
+        <v>24297.79981757338</v>
       </c>
       <c r="AD81" t="n">
-        <v>24362.63014426748</v>
+        <v>26430.81062768109</v>
       </c>
       <c r="AE81" t="n">
-        <v>23543.63038000182</v>
+        <v>26544.57882970003</v>
       </c>
     </row>
     <row r="82">
@@ -5334,22 +5334,22 @@
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>20940.83816879236</v>
+        <v>11851.70032198903</v>
       </c>
       <c r="AA82" t="n">
-        <v>13955.02699355712</v>
+        <v>8970.62714989137</v>
       </c>
       <c r="AB82" t="n">
-        <v>19675.88085080851</v>
+        <v>9401.705221925818</v>
       </c>
       <c r="AC82" t="n">
-        <v>20098.8175778484</v>
+        <v>15816.91727789308</v>
       </c>
       <c r="AD82" t="n">
-        <v>14213.99029359353</v>
+        <v>20666.99192533032</v>
       </c>
       <c r="AE82" t="n">
-        <v>16657.34392702167</v>
+        <v>20435.85809222482</v>
       </c>
     </row>
     <row r="83">
@@ -5393,22 +5393,22 @@
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>27987.83362316389</v>
+        <v>27369.13574908327</v>
       </c>
       <c r="AA83" t="n">
-        <v>25895.39370298607</v>
+        <v>30956.68629866216</v>
       </c>
       <c r="AB83" t="n">
-        <v>27974.93444903022</v>
+        <v>24111.11754615043</v>
       </c>
       <c r="AC83" t="n">
-        <v>26566.80808130878</v>
+        <v>31332.0885920721</v>
       </c>
       <c r="AD83" t="n">
-        <v>30469.21786832493</v>
+        <v>31208.536227558</v>
       </c>
       <c r="AE83" t="n">
-        <v>27799.79507810842</v>
+        <v>36565.77045955898</v>
       </c>
     </row>
     <row r="84">
@@ -5452,22 +5452,22 @@
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>306321.7877137941</v>
+        <v>82634.6041613954</v>
       </c>
       <c r="AA84" t="n">
-        <v>236735.0597165083</v>
+        <v>56642.41962577882</v>
       </c>
       <c r="AB84" t="n">
-        <v>311595.2331846427</v>
+        <v>80686.14666777634</v>
       </c>
       <c r="AC84" t="n">
-        <v>97728.22443025076</v>
+        <v>87160.55987869257</v>
       </c>
       <c r="AD84" t="n">
-        <v>92302.28791351274</v>
+        <v>66697.87645118097</v>
       </c>
       <c r="AE84" t="n">
-        <v>68899.44807182412</v>
+        <v>97724.42709202046</v>
       </c>
     </row>
     <row r="85">
@@ -5511,22 +5511,22 @@
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>20840.87723375421</v>
+        <v>33383.43520830817</v>
       </c>
       <c r="AA85" t="n">
-        <v>19367.06262868372</v>
+        <v>23061.74244486065</v>
       </c>
       <c r="AB85" t="n">
-        <v>24784.65288991781</v>
+        <v>27103.63326729773</v>
       </c>
       <c r="AC85" t="n">
-        <v>34761.31212549296</v>
+        <v>21802.39734696863</v>
       </c>
       <c r="AD85" t="n">
-        <v>21656.03835268278</v>
+        <v>31181.6593898887</v>
       </c>
       <c r="AE85" t="n">
-        <v>28790.53945398296</v>
+        <v>17842.24534386574</v>
       </c>
     </row>
     <row r="86">
@@ -5570,22 +5570,22 @@
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>13887.3226577654</v>
+        <v>11484.27328531778</v>
       </c>
       <c r="AA86" t="n">
-        <v>12638.80348863447</v>
+        <v>13974.72935047483</v>
       </c>
       <c r="AB86" t="n">
-        <v>12832.35603055801</v>
+        <v>19124.14485369863</v>
       </c>
       <c r="AC86" t="n">
-        <v>15728.91893646695</v>
+        <v>15115.78780332968</v>
       </c>
       <c r="AD86" t="n">
-        <v>13224.94681700915</v>
+        <v>12952.46005438376</v>
       </c>
       <c r="AE86" t="n">
-        <v>12290.23034727873</v>
+        <v>13925.22170371076</v>
       </c>
     </row>
     <row r="87">
@@ -5629,22 +5629,22 @@
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="n">
-        <v>49398.08369336391</v>
+        <v>55190.25230223686</v>
       </c>
       <c r="AA87" t="n">
-        <v>58047.40554556097</v>
+        <v>56696.55655083829</v>
       </c>
       <c r="AB87" t="n">
-        <v>71547.72874235777</v>
+        <v>76146.9807895398</v>
       </c>
       <c r="AC87" t="n">
-        <v>77059.89354795267</v>
+        <v>74356.48524118887</v>
       </c>
       <c r="AD87" t="n">
-        <v>55975.47991815693</v>
+        <v>73219.52484597196</v>
       </c>
       <c r="AE87" t="n">
-        <v>74093.66118096552</v>
+        <v>64964.16284116247</v>
       </c>
     </row>
     <row r="88">
@@ -5688,22 +5688,22 @@
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="n">
-        <v>27024.45062571286</v>
+        <v>8102.337636196654</v>
       </c>
       <c r="AA88" t="n">
-        <v>32813.35054218901</v>
+        <v>11467.34900356885</v>
       </c>
       <c r="AB88" t="n">
-        <v>26860.44743479889</v>
+        <v>10319.76639377536</v>
       </c>
       <c r="AC88" t="n">
-        <v>40743.45278809239</v>
+        <v>35771.7733046643</v>
       </c>
       <c r="AD88" t="n">
-        <v>29259.32950501487</v>
+        <v>33764.34479517961</v>
       </c>
       <c r="AE88" t="n">
-        <v>28325.97701340222</v>
+        <v>26002.33582919135</v>
       </c>
     </row>
     <row r="89">
@@ -5747,22 +5747,22 @@
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
-        <v>125534.4279801106</v>
+        <v>275898.8921091996</v>
       </c>
       <c r="AA89" t="n">
-        <v>120897.8043722228</v>
+        <v>419368.2401711798</v>
       </c>
       <c r="AB89" t="n">
-        <v>108467.9208409047</v>
+        <v>322619.3049441878</v>
       </c>
       <c r="AC89" t="n">
-        <v>121208.9129926379</v>
+        <v>112482.5316738576</v>
       </c>
       <c r="AD89" t="n">
-        <v>103133.3650536742</v>
+        <v>83224.56762153775</v>
       </c>
       <c r="AE89" t="n">
-        <v>93977.60184914924</v>
+        <v>103764.9423871019</v>
       </c>
     </row>
     <row r="90">
@@ -5806,22 +5806,22 @@
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="n">
-        <v>30257.88784024314</v>
+        <v>28259.35771079559</v>
       </c>
       <c r="AA90" t="n">
-        <v>25501.06103619181</v>
+        <v>22175.47504081493</v>
       </c>
       <c r="AB90" t="n">
-        <v>26866.01582832045</v>
+        <v>26631.93381111123</v>
       </c>
       <c r="AC90" t="n">
-        <v>29008.64922934229</v>
+        <v>21431.0068916453</v>
       </c>
       <c r="AD90" t="n">
-        <v>19352.44629485047</v>
+        <v>25230.39712079282</v>
       </c>
       <c r="AE90" t="n">
-        <v>24089.80319467525</v>
+        <v>31905.95993318947</v>
       </c>
     </row>
     <row r="91">
@@ -5865,22 +5865,22 @@
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="n">
-        <v>5811.58683145002</v>
+        <v>1785.21444290193</v>
       </c>
       <c r="AA91" t="n">
-        <v>5546.42530612086</v>
+        <v>1455.414670694867</v>
       </c>
       <c r="AB91" t="n">
-        <v>6332.27338234523</v>
+        <v>1600.751601610935</v>
       </c>
       <c r="AC91" t="n">
-        <v>7081.797405778879</v>
+        <v>6803.462763852545</v>
       </c>
       <c r="AD91" t="n">
-        <v>7098.732557266934</v>
+        <v>6838.58097698695</v>
       </c>
       <c r="AE91" t="n">
-        <v>7897.511411378337</v>
+        <v>5500.233304610052</v>
       </c>
     </row>
     <row r="92">
@@ -5924,22 +5924,22 @@
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="n">
-        <v>17331.87010158375</v>
+        <v>2875.579446408067</v>
       </c>
       <c r="AA92" t="n">
-        <v>21528.53676287663</v>
+        <v>2858.023576761785</v>
       </c>
       <c r="AB92" t="n">
-        <v>27554.44714965852</v>
+        <v>2345.38365488437</v>
       </c>
       <c r="AC92" t="n">
-        <v>6061.968654319</v>
+        <v>5358.545401051949</v>
       </c>
       <c r="AD92" t="n">
-        <v>6278.705208688272</v>
+        <v>6147.406766094005</v>
       </c>
       <c r="AE92" t="n">
-        <v>5892.197473773419</v>
+        <v>5897.601026667928</v>
       </c>
     </row>
     <row r="93">
@@ -5983,22 +5983,22 @@
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="n">
-        <v>73588.83586209035</v>
+        <v>92875.30348138453</v>
       </c>
       <c r="AA93" t="n">
-        <v>134363.4842312394</v>
+        <v>146180.1953655798</v>
       </c>
       <c r="AB93" t="n">
-        <v>104568.4139825674</v>
+        <v>112226.0197864836</v>
       </c>
       <c r="AC93" t="n">
-        <v>97375.24323099329</v>
+        <v>106778.2366889745</v>
       </c>
       <c r="AD93" t="n">
-        <v>110554.3510837942</v>
+        <v>112395.5637913759</v>
       </c>
       <c r="AE93" t="n">
-        <v>111209.1411325682</v>
+        <v>100062.9143494354</v>
       </c>
     </row>
     <row r="94">
@@ -6042,22 +6042,22 @@
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="n">
-        <v>113793.5811690183</v>
+        <v>87303.88174641697</v>
       </c>
       <c r="AA94" t="n">
-        <v>106646.1792752992</v>
+        <v>102776.2499711524</v>
       </c>
       <c r="AB94" t="n">
-        <v>168166.6021334299</v>
+        <v>110387.3675911962</v>
       </c>
       <c r="AC94" t="n">
-        <v>137142.2783907337</v>
+        <v>140680.8406510925</v>
       </c>
       <c r="AD94" t="n">
-        <v>85098.05376178074</v>
+        <v>155349.4779553209</v>
       </c>
       <c r="AE94" t="n">
-        <v>133049.1166225028</v>
+        <v>111622.6111448023</v>
       </c>
     </row>
     <row r="95">
@@ -6101,22 +6101,22 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="n">
-        <v>69570.84907577836</v>
+        <v>18557.58398279195</v>
       </c>
       <c r="AA95" t="n">
-        <v>42211.68844502146</v>
+        <v>19107.49996076086</v>
       </c>
       <c r="AB95" t="n">
-        <v>46780.60412591811</v>
+        <v>15259.1325095359</v>
       </c>
       <c r="AC95" t="n">
-        <v>15019.56090768726</v>
+        <v>22979.82562648636</v>
       </c>
       <c r="AD95" t="n">
-        <v>15851.47750301963</v>
+        <v>21409.87198531793</v>
       </c>
       <c r="AE95" t="n">
-        <v>13418.66509971461</v>
+        <v>22973.34320886267</v>
       </c>
     </row>
     <row r="96">
@@ -6160,22 +6160,22 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="n">
-        <v>16027.24426279701</v>
+        <v>13989.27542292517</v>
       </c>
       <c r="AA96" t="n">
-        <v>16327.31943482217</v>
+        <v>19732.2080579164</v>
       </c>
       <c r="AB96" t="n">
-        <v>12397.6251379615</v>
+        <v>16211.82107397362</v>
       </c>
       <c r="AC96" t="n">
-        <v>13328.0052804031</v>
+        <v>19652.66412630173</v>
       </c>
       <c r="AD96" t="n">
-        <v>18065.29492071635</v>
+        <v>14448.04747255472</v>
       </c>
       <c r="AE96" t="n">
-        <v>14918.28081762451</v>
+        <v>13841.53323411171</v>
       </c>
     </row>
     <row r="97">
@@ -6219,22 +6219,22 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="n">
-        <v>36368.21216900356</v>
+        <v>101757.942375167</v>
       </c>
       <c r="AA97" t="n">
-        <v>38259.8302245494</v>
+        <v>74137.77163053594</v>
       </c>
       <c r="AB97" t="n">
-        <v>39969.58864582991</v>
+        <v>100723.4570229324</v>
       </c>
       <c r="AC97" t="n">
-        <v>115494.5997469687</v>
+        <v>115689.5365404431</v>
       </c>
       <c r="AD97" t="n">
-        <v>62614.0611035538</v>
+        <v>106293.8347503813</v>
       </c>
       <c r="AE97" t="n">
-        <v>128164.697997337</v>
+        <v>101801.0976639328</v>
       </c>
     </row>
     <row r="98">
@@ -6278,22 +6278,22 @@
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="n">
-        <v>7806.533961471341</v>
+        <v>23237.10421568105</v>
       </c>
       <c r="AA98" t="n">
-        <v>8023.074821316716</v>
+        <v>17258.36400470467</v>
       </c>
       <c r="AB98" t="n">
-        <v>6195.122314330063</v>
+        <v>15997.79899757465</v>
       </c>
       <c r="AC98" t="n">
-        <v>8258.409903555705</v>
+        <v>7161.639331861804</v>
       </c>
       <c r="AD98" t="n">
-        <v>6910.697180685929</v>
+        <v>9730.527045120845</v>
       </c>
       <c r="AE98" t="n">
-        <v>7426.472748117065</v>
+        <v>5498.725409009522</v>
       </c>
     </row>
     <row r="99">
@@ -6337,22 +6337,22 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="n">
-        <v>7123.320286603568</v>
+        <v>9191.268128311282</v>
       </c>
       <c r="AA99" t="n">
-        <v>8984.228788168823</v>
+        <v>8448.396931246494</v>
       </c>
       <c r="AB99" t="n">
-        <v>8042.615368551456</v>
+        <v>8838.480797884356</v>
       </c>
       <c r="AC99" t="n">
-        <v>11252.91769301262</v>
+        <v>9491.775876995944</v>
       </c>
       <c r="AD99" t="n">
-        <v>7542.227669685761</v>
+        <v>12080.47354132895</v>
       </c>
       <c r="AE99" t="n">
-        <v>9094.816878269099</v>
+        <v>11903.89117627848</v>
       </c>
     </row>
     <row r="100">
@@ -6396,22 +6396,22 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="n">
-        <v>40083.8300083726</v>
+        <v>46973.86947632034</v>
       </c>
       <c r="AA100" t="n">
-        <v>46563.69046843822</v>
+        <v>38763.66170441572</v>
       </c>
       <c r="AB100" t="n">
-        <v>44483.86373471299</v>
+        <v>48663.37645140734</v>
       </c>
       <c r="AC100" t="n">
-        <v>40238.34344835858</v>
+        <v>47021.02990738964</v>
       </c>
       <c r="AD100" t="n">
-        <v>47288.02352212412</v>
+        <v>34861.09788040718</v>
       </c>
       <c r="AE100" t="n">
-        <v>45503.56946468767</v>
+        <v>45877.25142950552</v>
       </c>
     </row>
     <row r="101">
@@ -6455,22 +6455,22 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="n">
-        <v>5433.131734461614</v>
+        <v>15363.91079367735</v>
       </c>
       <c r="AA101" t="n">
-        <v>4582.901790955209</v>
+        <v>16768.96390571124</v>
       </c>
       <c r="AB101" t="n">
-        <v>5817.85365960109</v>
+        <v>17400.92140263214</v>
       </c>
       <c r="AC101" t="n">
-        <v>12488.42570761118</v>
+        <v>15116.94485610574</v>
       </c>
       <c r="AD101" t="n">
-        <v>13414.98687288115</v>
+        <v>12918.49016826914</v>
       </c>
       <c r="AE101" t="n">
-        <v>16979.0526064831</v>
+        <v>14443.79082849731</v>
       </c>
     </row>
     <row r="102">
@@ -6514,22 +6514,22 @@
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="n">
-        <v>21632.73672630256</v>
+        <v>23727.44891748806</v>
       </c>
       <c r="AA102" t="n">
-        <v>21874.25023488413</v>
+        <v>22722.867863441</v>
       </c>
       <c r="AB102" t="n">
-        <v>19961.3459157676</v>
+        <v>25559.22685290843</v>
       </c>
       <c r="AC102" t="n">
-        <v>21137.68094860836</v>
+        <v>22348.0145460413</v>
       </c>
       <c r="AD102" t="n">
-        <v>23282.82483957705</v>
+        <v>27381.31023136303</v>
       </c>
       <c r="AE102" t="n">
-        <v>16240.41437913044</v>
+        <v>23889.87743171521</v>
       </c>
     </row>
     <row r="103">
@@ -6573,22 +6573,22 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="n">
-        <v>21060.99477239752</v>
+        <v>16828.95362492597</v>
       </c>
       <c r="AA103" t="n">
-        <v>18123.29849758636</v>
+        <v>14332.89884672805</v>
       </c>
       <c r="AB103" t="n">
-        <v>21691.32897424834</v>
+        <v>18814.70610227123</v>
       </c>
       <c r="AC103" t="n">
-        <v>18993.68427027543</v>
+        <v>21165.33691354104</v>
       </c>
       <c r="AD103" t="n">
-        <v>20360.99142759287</v>
+        <v>15959.58620798707</v>
       </c>
       <c r="AE103" t="n">
-        <v>14533.44943388001</v>
+        <v>15139.82831552144</v>
       </c>
     </row>
     <row r="104">
@@ -6632,22 +6632,22 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="n">
-        <v>32508.97008119134</v>
+        <v>30050.44765099814</v>
       </c>
       <c r="AA104" t="n">
-        <v>25724.2887002343</v>
+        <v>33352.43656964525</v>
       </c>
       <c r="AB104" t="n">
-        <v>36724.54870614231</v>
+        <v>27195.79785171959</v>
       </c>
       <c r="AC104" t="n">
-        <v>31239.0082174803</v>
+        <v>30597.76211884577</v>
       </c>
       <c r="AD104" t="n">
-        <v>40660.33900725743</v>
+        <v>25316.03779453741</v>
       </c>
       <c r="AE104" t="n">
-        <v>31860.37145783583</v>
+        <v>36862.65139232398</v>
       </c>
     </row>
     <row r="105">
@@ -6691,22 +6691,22 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="n">
-        <v>46736.58633391533</v>
+        <v>92688.36912845701</v>
       </c>
       <c r="AA105" t="n">
-        <v>33440.13068754092</v>
+        <v>82524.5437608888</v>
       </c>
       <c r="AB105" t="n">
-        <v>52442.8314745197</v>
+        <v>76490.89837222498</v>
       </c>
       <c r="AC105" t="n">
-        <v>106674.1279430156</v>
+        <v>80667.3204231967</v>
       </c>
       <c r="AD105" t="n">
-        <v>87294.3106640957</v>
+        <v>83663.05337070061</v>
       </c>
       <c r="AE105" t="n">
-        <v>80841.87595531845</v>
+        <v>85723.6599279675</v>
       </c>
     </row>
     <row r="106">
@@ -6750,22 +6750,22 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="n">
-        <v>21749.13062746945</v>
+        <v>27273.31902572131</v>
       </c>
       <c r="AA106" t="n">
-        <v>26727.47287976092</v>
+        <v>29194.9780665432</v>
       </c>
       <c r="AB106" t="n">
-        <v>26107.99629829045</v>
+        <v>25394.18888088244</v>
       </c>
       <c r="AC106" t="n">
-        <v>22842.87069745847</v>
+        <v>22661.30100333596</v>
       </c>
       <c r="AD106" t="n">
-        <v>25514.22866379215</v>
+        <v>25683.88196711185</v>
       </c>
       <c r="AE106" t="n">
-        <v>29360.0062685451</v>
+        <v>23387.90949677565</v>
       </c>
     </row>
     <row r="107">
@@ -6809,22 +6809,22 @@
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="n">
-        <v>182180.29172375</v>
+        <v>39532.46916646868</v>
       </c>
       <c r="AA107" t="n">
-        <v>151060.6847761473</v>
+        <v>38169.82888702348</v>
       </c>
       <c r="AB107" t="n">
-        <v>195358.9833098033</v>
+        <v>44392.72121719693</v>
       </c>
       <c r="AC107" t="n">
-        <v>44211.66574158608</v>
+        <v>46121.07809314744</v>
       </c>
       <c r="AD107" t="n">
-        <v>33563.03096820326</v>
+        <v>41298.41032487448</v>
       </c>
       <c r="AE107" t="n">
-        <v>40001.11608349028</v>
+        <v>38956.09224600625</v>
       </c>
     </row>
     <row r="108">
@@ -6868,22 +6868,22 @@
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="n">
-        <v>10409.79163152732</v>
+        <v>3065.613487297056</v>
       </c>
       <c r="AA108" t="n">
-        <v>6994.081433091341</v>
+        <v>2576.882480788443</v>
       </c>
       <c r="AB108" t="n">
-        <v>6148.982124463473</v>
+        <v>3438.970958721846</v>
       </c>
       <c r="AC108" t="n">
-        <v>2444.34831012266</v>
+        <v>2836.360209045049</v>
       </c>
       <c r="AD108" t="n">
-        <v>3389.338109794893</v>
+        <v>2571.496633119685</v>
       </c>
       <c r="AE108" t="n">
-        <v>2121.011313544555</v>
+        <v>2598.605381988131</v>
       </c>
     </row>
     <row r="109">
@@ -6927,22 +6927,22 @@
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="n">
-        <v>18137.9039797618</v>
+        <v>8165.559424021327</v>
       </c>
       <c r="AA109" t="n">
-        <v>20678.6026770483</v>
+        <v>9216.273676990051</v>
       </c>
       <c r="AB109" t="n">
-        <v>20002.16138157052</v>
+        <v>10022.15362600693</v>
       </c>
       <c r="AC109" t="n">
-        <v>22445.13553589787</v>
+        <v>22077.47406463051</v>
       </c>
       <c r="AD109" t="n">
-        <v>18717.33297989447</v>
+        <v>18961.19362649236</v>
       </c>
       <c r="AE109" t="n">
-        <v>17345.34605596554</v>
+        <v>23283.07986762316</v>
       </c>
     </row>
     <row r="110">
@@ -6986,22 +6986,22 @@
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="n">
-        <v>8296.718725562734</v>
+        <v>9312.737862168597</v>
       </c>
       <c r="AA110" t="n">
-        <v>11225.82894857882</v>
+        <v>10627.58971587094</v>
       </c>
       <c r="AB110" t="n">
-        <v>8322.508087887953</v>
+        <v>9292.244729759581</v>
       </c>
       <c r="AC110" t="n">
-        <v>9482.810449538312</v>
+        <v>10480.60427496273</v>
       </c>
       <c r="AD110" t="n">
-        <v>8713.742055619876</v>
+        <v>8517.849399361008</v>
       </c>
       <c r="AE110" t="n">
-        <v>6274.934506676837</v>
+        <v>9849.300901918001</v>
       </c>
     </row>
     <row r="111">
@@ -7045,22 +7045,22 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="n">
-        <v>7954.989254811052</v>
+        <v>2975.255322138995</v>
       </c>
       <c r="AA111" t="n">
-        <v>4624.281390144092</v>
+        <v>2809.81011455131</v>
       </c>
       <c r="AB111" t="n">
-        <v>6628.082454152026</v>
+        <v>2179.88281277875</v>
       </c>
       <c r="AC111" t="n">
-        <v>5818.018034539541</v>
+        <v>6154.634905603682</v>
       </c>
       <c r="AD111" t="n">
-        <v>6488.909516248705</v>
+        <v>5705.925614239178</v>
       </c>
       <c r="AE111" t="n">
-        <v>6285.923887224493</v>
+        <v>7179.242540943072</v>
       </c>
     </row>
     <row r="112">
@@ -7104,22 +7104,22 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="n">
-        <v>3960.762199393998</v>
+        <v>6787.843545591616</v>
       </c>
       <c r="AA112" t="n">
-        <v>3256.46508026363</v>
+        <v>7108.226366315748</v>
       </c>
       <c r="AB112" t="n">
-        <v>3741.25342803394</v>
+        <v>8725.295751529846</v>
       </c>
       <c r="AC112" t="n">
-        <v>8834.972116706471</v>
+        <v>10252.58202391142</v>
       </c>
       <c r="AD112" t="n">
-        <v>7240.278715611961</v>
+        <v>12888.52377646079</v>
       </c>
       <c r="AE112" t="n">
-        <v>8898.072987172995</v>
+        <v>9141.030732044253</v>
       </c>
     </row>
     <row r="113">
@@ -7163,22 +7163,22 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="n">
-        <v>7815.431316379233</v>
+        <v>12983.12491949195</v>
       </c>
       <c r="AA113" t="n">
-        <v>5512.917517780073</v>
+        <v>17095.69104882794</v>
       </c>
       <c r="AB113" t="n">
-        <v>6175.582858397767</v>
+        <v>16292.51760102911</v>
       </c>
       <c r="AC113" t="n">
-        <v>15340.47742505534</v>
+        <v>16692.30226325045</v>
       </c>
       <c r="AD113" t="n">
-        <v>16320.74151801077</v>
+        <v>16489.89783525795</v>
       </c>
       <c r="AE113" t="n">
-        <v>14797.40568498684</v>
+        <v>17032.12474942389</v>
       </c>
     </row>
     <row r="114">
@@ -7222,22 +7222,22 @@
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="n">
-        <v>51509.53347668936</v>
+        <v>171346.0035342779</v>
       </c>
       <c r="AA114" t="n">
-        <v>68533.59708225139</v>
+        <v>183252.7828080794</v>
       </c>
       <c r="AB114" t="n">
-        <v>73001.02596790435</v>
+        <v>207618.0819498847</v>
       </c>
       <c r="AC114" t="n">
-        <v>52858.7887162568</v>
+        <v>45737.80964354944</v>
       </c>
       <c r="AD114" t="n">
-        <v>63641.59107354018</v>
+        <v>62875.78550949247</v>
       </c>
       <c r="AE114" t="n">
-        <v>64714.10081293261</v>
+        <v>51692.87469404788</v>
       </c>
     </row>
     <row r="115">
@@ -7281,22 +7281,22 @@
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="n">
-        <v>3275.347705565172</v>
+        <v>8350.682065076919</v>
       </c>
       <c r="AA115" t="n">
-        <v>2747.125917053355</v>
+        <v>12276.37955431622</v>
       </c>
       <c r="AB115" t="n">
-        <v>2566.926393093173</v>
+        <v>10866.683206052</v>
       </c>
       <c r="AC115" t="n">
-        <v>7625.921667526474</v>
+        <v>7258.678024421872</v>
       </c>
       <c r="AD115" t="n">
-        <v>6109.177060539194</v>
+        <v>5432.994107866202</v>
       </c>
       <c r="AE115" t="n">
-        <v>6998.039082611661</v>
+        <v>8168.716353799496</v>
       </c>
     </row>
     <row r="116">
@@ -7340,22 +7340,22 @@
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="n">
-        <v>23163.99390253079</v>
+        <v>20514.59425208247</v>
       </c>
       <c r="AA116" t="n">
-        <v>25482.03769102172</v>
+        <v>18344.24769605993</v>
       </c>
       <c r="AB116" t="n">
-        <v>24165.96072026987</v>
+        <v>23589.67074341454</v>
       </c>
       <c r="AC116" t="n">
-        <v>22378.69327850618</v>
+        <v>21068.19383550038</v>
       </c>
       <c r="AD116" t="n">
-        <v>17895.36210482765</v>
+        <v>22086.85669742564</v>
       </c>
       <c r="AE116" t="n">
-        <v>22138.49503657235</v>
+        <v>17951.73290867374</v>
       </c>
     </row>
     <row r="117">
@@ -7399,22 +7399,22 @@
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="n">
-        <v>14108.9537162304</v>
+        <v>15187.76808517048</v>
       </c>
       <c r="AA117" t="n">
-        <v>11439.25829864549</v>
+        <v>14512.69247754144</v>
       </c>
       <c r="AB117" t="n">
-        <v>13108.15935963153</v>
+        <v>12584.69793701302</v>
       </c>
       <c r="AC117" t="n">
-        <v>13085.3184296469</v>
+        <v>10588.94980569844</v>
       </c>
       <c r="AD117" t="n">
-        <v>13323.16025742555</v>
+        <v>12195.1970582904</v>
       </c>
       <c r="AE117" t="n">
-        <v>9853.938643678484</v>
+        <v>16398.92667789681</v>
       </c>
     </row>
     <row r="118">
@@ -7458,22 +7458,22 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="n">
-        <v>20071.06709202653</v>
+        <v>34517.25140058845</v>
       </c>
       <c r="AA118" t="n">
-        <v>13418.59250130326</v>
+        <v>31919.01820011235</v>
       </c>
       <c r="AB118" t="n">
-        <v>16053.52770051576</v>
+        <v>32785.35550077816</v>
       </c>
       <c r="AC118" t="n">
-        <v>11587.8134707084</v>
+        <v>13569.37031736679</v>
       </c>
       <c r="AD118" t="n">
-        <v>17740.95772367873</v>
+        <v>10663.3793043922</v>
       </c>
       <c r="AE118" t="n">
-        <v>17412.0738277276</v>
+        <v>19487.19813862742</v>
       </c>
     </row>
     <row r="119">
@@ -7517,22 +7517,22 @@
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="n">
-        <v>17034.94073710724</v>
+        <v>61847.46171418536</v>
       </c>
       <c r="AA119" t="n">
-        <v>19234.474221107</v>
+        <v>49531.42659268039</v>
       </c>
       <c r="AB119" t="n">
-        <v>18001.13201964265</v>
+        <v>62910.96491381092</v>
       </c>
       <c r="AC119" t="n">
-        <v>52503.0594703611</v>
+        <v>51513.5959687259</v>
       </c>
       <c r="AD119" t="n">
-        <v>45299.87311209595</v>
+        <v>48827.86503899559</v>
       </c>
       <c r="AE119" t="n">
-        <v>65255.25508094032</v>
+        <v>52835.25759950035</v>
       </c>
     </row>
     <row r="120">
@@ -7576,22 +7576,22 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="n">
-        <v>32759.46223748805</v>
+        <v>44422.35272594406</v>
       </c>
       <c r="AA120" t="n">
-        <v>38057.61926138692</v>
+        <v>41990.07070273951</v>
       </c>
       <c r="AB120" t="n">
-        <v>40350.70101478225</v>
+        <v>35518.76935556141</v>
       </c>
       <c r="AC120" t="n">
-        <v>36266.67024254579</v>
+        <v>38022.80669285238</v>
       </c>
       <c r="AD120" t="n">
-        <v>32109.28549133965</v>
+        <v>28753.72591887782</v>
       </c>
       <c r="AE120" t="n">
-        <v>39518.49908520907</v>
+        <v>52707.15419740856</v>
       </c>
     </row>
     <row r="121">
@@ -7635,22 +7635,22 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="n">
-        <v>20179.16850564526</v>
+        <v>290851.014688218</v>
       </c>
       <c r="AA121" t="n">
-        <v>23435.36635877297</v>
+        <v>247127.6284282259</v>
       </c>
       <c r="AB121" t="n">
-        <v>25706.18364540368</v>
+        <v>247218.8304289265</v>
       </c>
       <c r="AC121" t="n">
-        <v>75698.99823754486</v>
+        <v>80524.80331079384</v>
       </c>
       <c r="AD121" t="n">
-        <v>95691.01137990705</v>
+        <v>59869.98304665068</v>
       </c>
       <c r="AE121" t="n">
-        <v>97209.14494691856</v>
+        <v>97413.65256548242</v>
       </c>
     </row>
     <row r="122">
@@ -7694,22 +7694,22 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="n">
-        <v>20198.11199337433</v>
+        <v>18678.41075001451</v>
       </c>
       <c r="AA122" t="n">
-        <v>18349.24433738563</v>
+        <v>17212.61459267342</v>
       </c>
       <c r="AB122" t="n">
-        <v>24163.61867411367</v>
+        <v>19662.62538445361</v>
       </c>
       <c r="AC122" t="n">
-        <v>23219.5635727049</v>
+        <v>17943.25443159428</v>
       </c>
       <c r="AD122" t="n">
-        <v>19653.45906956322</v>
+        <v>15775.13861862545</v>
       </c>
       <c r="AE122" t="n">
-        <v>15847.54862214783</v>
+        <v>21832.7228560678</v>
       </c>
     </row>
     <row r="123">
@@ -7753,22 +7753,22 @@
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="n">
-        <v>8683.617882048393</v>
+        <v>13454.85480254624</v>
       </c>
       <c r="AA123" t="n">
-        <v>11450.38860030215</v>
+        <v>13653.26840693398</v>
       </c>
       <c r="AB123" t="n">
-        <v>11504.57890337861</v>
+        <v>9257.071622596506</v>
       </c>
       <c r="AC123" t="n">
-        <v>10714.10870028438</v>
+        <v>12052.32279185124</v>
       </c>
       <c r="AD123" t="n">
-        <v>11682.56835536882</v>
+        <v>13397.19640091779</v>
       </c>
       <c r="AE123" t="n">
-        <v>14844.29204486561</v>
+        <v>11028.74931452863</v>
       </c>
     </row>
     <row r="124">
@@ -7812,22 +7812,22 @@
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="n">
-        <v>19375.44493833649</v>
+        <v>17853.59525700211</v>
       </c>
       <c r="AA124" t="n">
-        <v>18031.20317587533</v>
+        <v>16482.31587331641</v>
       </c>
       <c r="AB124" t="n">
-        <v>19236.66199192522</v>
+        <v>16382.27136129904</v>
       </c>
       <c r="AC124" t="n">
-        <v>21362.83097377149</v>
+        <v>18529.55839865423</v>
       </c>
       <c r="AD124" t="n">
-        <v>23273.37783832143</v>
+        <v>17491.59498496868</v>
       </c>
       <c r="AE124" t="n">
-        <v>15248.35671976119</v>
+        <v>17044.0638259265</v>
       </c>
     </row>
     <row r="125">
@@ -7871,22 +7871,22 @@
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="n">
-        <v>25891.78701233015</v>
+        <v>24757.58183114071</v>
       </c>
       <c r="AA125" t="n">
-        <v>31544.73258877585</v>
+        <v>28206.6471127096</v>
       </c>
       <c r="AB125" t="n">
-        <v>23620.42575769199</v>
+        <v>34827.52607460364</v>
       </c>
       <c r="AC125" t="n">
-        <v>28332.15014598098</v>
+        <v>29433.94772949522</v>
       </c>
       <c r="AD125" t="n">
-        <v>30115.03139699176</v>
+        <v>34066.89448948023</v>
       </c>
       <c r="AE125" t="n">
-        <v>31409.95721391319</v>
+        <v>27203.07962045464</v>
       </c>
     </row>
     <row r="126">
@@ -7930,22 +7930,22 @@
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="n">
-        <v>31217.84787647352</v>
+        <v>9818.256518530705</v>
       </c>
       <c r="AA126" t="n">
-        <v>29662.07582932323</v>
+        <v>11175.68719587937</v>
       </c>
       <c r="AB126" t="n">
-        <v>25936.11938668902</v>
+        <v>9016.819698480846</v>
       </c>
       <c r="AC126" t="n">
-        <v>26427.42389615412</v>
+        <v>27946.51061756195</v>
       </c>
       <c r="AD126" t="n">
-        <v>29005.95869254108</v>
+        <v>27951.34907859375</v>
       </c>
       <c r="AE126" t="n">
-        <v>20403.69323324445</v>
+        <v>27865.73140727672</v>
       </c>
     </row>
     <row r="127">
@@ -7989,22 +7989,22 @@
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="n">
-        <v>5200.306691846494</v>
+        <v>5964.207401689787</v>
       </c>
       <c r="AA127" t="n">
-        <v>5840.847169708554</v>
+        <v>6786.306003268429</v>
       </c>
       <c r="AB127" t="n">
-        <v>8575.420832438833</v>
+        <v>5421.423836640044</v>
       </c>
       <c r="AC127" t="n">
-        <v>7348.80108055462</v>
+        <v>8168.431021396312</v>
       </c>
       <c r="AD127" t="n">
-        <v>11183.82432731055</v>
+        <v>8374.911183015069</v>
       </c>
       <c r="AE127" t="n">
-        <v>6477.385428546958</v>
+        <v>9189.252457650868</v>
       </c>
     </row>
     <row r="128">
@@ -8048,22 +8048,22 @@
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="n">
-        <v>21429.09624940894</v>
+        <v>21105.09381934616</v>
       </c>
       <c r="AA128" t="n">
-        <v>17212.64381602709</v>
+        <v>25878.30432090949</v>
       </c>
       <c r="AB128" t="n">
-        <v>27457.2376099138</v>
+        <v>18237.09542033084</v>
       </c>
       <c r="AC128" t="n">
-        <v>24126.33398445899</v>
+        <v>17576.12595528406</v>
       </c>
       <c r="AD128" t="n">
-        <v>23351.56064513507</v>
+        <v>21064.72737682937</v>
       </c>
       <c r="AE128" t="n">
-        <v>30270.98913747568</v>
+        <v>24777.39226831394</v>
       </c>
     </row>
     <row r="129">
@@ -8107,22 +8107,22 @@
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="n">
-        <v>59450.03951967867</v>
+        <v>26226.50519201235</v>
       </c>
       <c r="AA129" t="n">
-        <v>88976.14679086638</v>
+        <v>25545.34731982668</v>
       </c>
       <c r="AB129" t="n">
-        <v>79031.61564885046</v>
+        <v>27794.53846057013</v>
       </c>
       <c r="AC129" t="n">
-        <v>35812.33193732009</v>
+        <v>26201.25507687168</v>
       </c>
       <c r="AD129" t="n">
-        <v>24551.93418345731</v>
+        <v>29936.11749166433</v>
       </c>
       <c r="AE129" t="n">
-        <v>26611.3569507975</v>
+        <v>24137.25524533849</v>
       </c>
     </row>
     <row r="130">
@@ -8166,22 +8166,22 @@
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="n">
-        <v>613002.8249073421</v>
+        <v>308048.2761564055</v>
       </c>
       <c r="AA130" t="n">
-        <v>829201.117463483</v>
+        <v>256716.666106253</v>
       </c>
       <c r="AB130" t="n">
-        <v>792555.9147459965</v>
+        <v>274336.7455805147</v>
       </c>
       <c r="AC130" t="n">
-        <v>192823.8638242709</v>
+        <v>196898.2797381482</v>
       </c>
       <c r="AD130" t="n">
-        <v>291164.4472230995</v>
+        <v>304608.0577518671</v>
       </c>
       <c r="AE130" t="n">
-        <v>309731.920052336</v>
+        <v>309012.8364392592</v>
       </c>
     </row>
     <row r="131">
@@ -8225,22 +8225,22 @@
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="n">
-        <v>149342.0357955972</v>
+        <v>186271.410614923</v>
       </c>
       <c r="AA131" t="n">
-        <v>123469.7120427228</v>
+        <v>176529.0987581915</v>
       </c>
       <c r="AB131" t="n">
-        <v>154888.3196212809</v>
+        <v>141379.4914914038</v>
       </c>
       <c r="AC131" t="n">
-        <v>106575.9067420877</v>
+        <v>144676.2259607886</v>
       </c>
       <c r="AD131" t="n">
-        <v>153690.0614896365</v>
+        <v>131972.324597558</v>
       </c>
       <c r="AE131" t="n">
-        <v>149102.2989662798</v>
+        <v>165217.360652134</v>
       </c>
     </row>
     <row r="132">
@@ -8284,22 +8284,22 @@
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="n">
-        <v>9135.038246604117</v>
+        <v>7626.844105487377</v>
       </c>
       <c r="AA132" t="n">
-        <v>7099.512072318996</v>
+        <v>8027.823640008011</v>
       </c>
       <c r="AB132" t="n">
-        <v>11235.1505900131</v>
+        <v>11258.57257118221</v>
       </c>
       <c r="AC132" t="n">
-        <v>8649.709579887121</v>
+        <v>9377.436436252236</v>
       </c>
       <c r="AD132" t="n">
-        <v>8671.086166514406</v>
+        <v>10205.55751223172</v>
       </c>
       <c r="AE132" t="n">
-        <v>9237.374008607851</v>
+        <v>10352.21285967768</v>
       </c>
     </row>
     <row r="133">
@@ -8343,22 +8343,22 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="n">
-        <v>15908.5185580444</v>
+        <v>6510.618107824835</v>
       </c>
       <c r="AA133" t="n">
-        <v>16772.09649481387</v>
+        <v>4274.184095301496</v>
       </c>
       <c r="AB133" t="n">
-        <v>17257.81756537154</v>
+        <v>4110.666225146409</v>
       </c>
       <c r="AC133" t="n">
-        <v>16560.83452583144</v>
+        <v>19330.63611180151</v>
       </c>
       <c r="AD133" t="n">
-        <v>14154.0642151716</v>
+        <v>17989.52282684</v>
       </c>
       <c r="AE133" t="n">
-        <v>20276.02002455681</v>
+        <v>18479.94694831854</v>
       </c>
     </row>
     <row r="134">
@@ -8402,22 +8402,22 @@
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="n">
-        <v>4977.486219898115</v>
+        <v>4361.086084576256</v>
       </c>
       <c r="AA134" t="n">
-        <v>5861.63428618027</v>
+        <v>6491.173093788986</v>
       </c>
       <c r="AB134" t="n">
-        <v>4832.906139132695</v>
+        <v>5409.695466076749</v>
       </c>
       <c r="AC134" t="n">
-        <v>5653.746274663637</v>
+        <v>6091.82603358183</v>
       </c>
       <c r="AD134" t="n">
-        <v>7208.633338476367</v>
+        <v>4694.397732815763</v>
       </c>
       <c r="AE134" t="n">
-        <v>4919.977195748835</v>
+        <v>4894.751456197858</v>
       </c>
     </row>
     <row r="135">
@@ -8461,22 +8461,22 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="n">
-        <v>37218.61913875407</v>
+        <v>13101.70363629757</v>
       </c>
       <c r="AA135" t="n">
-        <v>47273.0371011446</v>
+        <v>17884.54442539046</v>
       </c>
       <c r="AB135" t="n">
-        <v>37965.47154067738</v>
+        <v>15421.35808670754</v>
       </c>
       <c r="AC135" t="n">
-        <v>13098.54017216887</v>
+        <v>12578.05921951324</v>
       </c>
       <c r="AD135" t="n">
-        <v>12814.33194322652</v>
+        <v>10310.08396688781</v>
       </c>
       <c r="AE135" t="n">
-        <v>9341.127767344036</v>
+        <v>10614.16396187083</v>
       </c>
     </row>
     <row r="136">
@@ -8520,22 +8520,22 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="n">
-        <v>7207.808354500724</v>
+        <v>29612.2085409995</v>
       </c>
       <c r="AA136" t="n">
-        <v>9060.188940261149</v>
+        <v>28419.03976472519</v>
       </c>
       <c r="AB136" t="n">
-        <v>5402.469597942842</v>
+        <v>25500.10602182708</v>
       </c>
       <c r="AC136" t="n">
-        <v>28508.80074498998</v>
+        <v>28016.55437082888</v>
       </c>
       <c r="AD136" t="n">
-        <v>27058.65500679801</v>
+        <v>25285.4839669026</v>
       </c>
       <c r="AE136" t="n">
-        <v>26772.19130207231</v>
+        <v>26512.61639334607</v>
       </c>
     </row>
     <row r="137">
@@ -8579,22 +8579,22 @@
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="n">
-        <v>81787.61187270746</v>
+        <v>55894.30340209757</v>
       </c>
       <c r="AA137" t="n">
-        <v>69570.51464477451</v>
+        <v>55013.17135881475</v>
       </c>
       <c r="AB137" t="n">
-        <v>77908.19936653115</v>
+        <v>69486.14395480379</v>
       </c>
       <c r="AC137" t="n">
-        <v>85708.74787017662</v>
+        <v>79112.62805844209</v>
       </c>
       <c r="AD137" t="n">
-        <v>84393.28925533681</v>
+        <v>74520.49388002501</v>
       </c>
       <c r="AE137" t="n">
-        <v>79900.09975034818</v>
+        <v>57557.17805308347</v>
       </c>
     </row>
     <row r="138">
@@ -8638,22 +8638,22 @@
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="n">
-        <v>11734.82338405295</v>
+        <v>33687.63467961191</v>
       </c>
       <c r="AA138" t="n">
-        <v>9292.348225417594</v>
+        <v>27975.06846075915</v>
       </c>
       <c r="AB138" t="n">
-        <v>6146.599238298018</v>
+        <v>26178.86773347627</v>
       </c>
       <c r="AC138" t="n">
-        <v>12399.92214233297</v>
+        <v>9815.60275713905</v>
       </c>
       <c r="AD138" t="n">
-        <v>10451.95571373322</v>
+        <v>11158.62078332943</v>
       </c>
       <c r="AE138" t="n">
-        <v>11273.86538438737</v>
+        <v>11008.89051513536</v>
       </c>
     </row>
     <row r="139">
@@ -8697,22 +8697,22 @@
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="n">
-        <v>3355.795211790101</v>
+        <v>3357.281684607117</v>
       </c>
       <c r="AA139" t="n">
-        <v>3172.915141558226</v>
+        <v>3521.715710255096</v>
       </c>
       <c r="AB139" t="n">
-        <v>2445.901003094</v>
+        <v>3214.686444836726</v>
       </c>
       <c r="AC139" t="n">
-        <v>11771.80135234951</v>
+        <v>11448.85108716727</v>
       </c>
       <c r="AD139" t="n">
-        <v>11025.00708543332</v>
+        <v>10167.73433899184</v>
       </c>
       <c r="AE139" t="n">
-        <v>9052.487152312691</v>
+        <v>11308.79750938287</v>
       </c>
     </row>
     <row r="140">
@@ -8756,22 +8756,22 @@
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="n">
-        <v>1158.016760492817</v>
+        <v>2374.698911923527</v>
       </c>
       <c r="AA140" t="n">
-        <v>1018.508325274558</v>
+        <v>2500.440997020387</v>
       </c>
       <c r="AB140" t="n">
-        <v>1139.961085650866</v>
+        <v>2449.824502910192</v>
       </c>
       <c r="AC140" t="n">
-        <v>2972.354284396839</v>
+        <v>2982.840811353918</v>
       </c>
       <c r="AD140" t="n">
-        <v>2799.096319538292</v>
+        <v>2582.979280198399</v>
       </c>
       <c r="AE140" t="n">
-        <v>2307.822209426825</v>
+        <v>2408.387738846571</v>
       </c>
     </row>
     <row r="141">
@@ -8815,22 +8815,22 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="n">
-        <v>19570.85560317828</v>
+        <v>15944.53183484531</v>
       </c>
       <c r="AA141" t="n">
-        <v>16075.85753554813</v>
+        <v>15840.51017974246</v>
       </c>
       <c r="AB141" t="n">
-        <v>20109.81895608383</v>
+        <v>23189.54644880777</v>
       </c>
       <c r="AC141" t="n">
-        <v>19501.19196258106</v>
+        <v>17217.27256070022</v>
       </c>
       <c r="AD141" t="n">
-        <v>15422.02157273175</v>
+        <v>20392.34032125544</v>
       </c>
       <c r="AE141" t="n">
-        <v>17155.53047137523</v>
+        <v>12015.96253176019</v>
       </c>
     </row>
     <row r="142">
@@ -8874,22 +8874,22 @@
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="n">
-        <v>10330.40309930284</v>
+        <v>6901.14829729763</v>
       </c>
       <c r="AA142" t="n">
-        <v>10351.62649652899</v>
+        <v>8304.225490759685</v>
       </c>
       <c r="AB142" t="n">
-        <v>6394.677425831946</v>
+        <v>10028.57291786429</v>
       </c>
       <c r="AC142" t="n">
-        <v>6997.884262402285</v>
+        <v>8590.716169979494</v>
       </c>
       <c r="AD142" t="n">
-        <v>8026.305940105491</v>
+        <v>8352.483471331949</v>
       </c>
       <c r="AE142" t="n">
-        <v>7206.690783804142</v>
+        <v>6313.768271413125</v>
       </c>
     </row>
     <row r="143">
@@ -8933,22 +8933,22 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="n">
-        <v>5879.809203649525</v>
+        <v>13832.05686865643</v>
       </c>
       <c r="AA143" t="n">
-        <v>7786.283803358533</v>
+        <v>14033.97815068739</v>
       </c>
       <c r="AB143" t="n">
-        <v>5353.620882243738</v>
+        <v>12334.67509932369</v>
       </c>
       <c r="AC143" t="n">
-        <v>14403.59487469055</v>
+        <v>14359.55391834732</v>
       </c>
       <c r="AD143" t="n">
-        <v>17283.43476612895</v>
+        <v>16372.24153855269</v>
       </c>
       <c r="AE143" t="n">
-        <v>10553.0852229171</v>
+        <v>15347.17459106344</v>
       </c>
     </row>
     <row r="144">
@@ -8992,22 +8992,22 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="n">
-        <v>8752.343211337267</v>
+        <v>32105.22791032746</v>
       </c>
       <c r="AA144" t="n">
-        <v>10867.65824828362</v>
+        <v>26396.85009084108</v>
       </c>
       <c r="AB144" t="n">
-        <v>11256.71783298227</v>
+        <v>43954.92000514884</v>
       </c>
       <c r="AC144" t="n">
-        <v>9318.259955722237</v>
+        <v>7942.00029839359</v>
       </c>
       <c r="AD144" t="n">
-        <v>9828.738479299194</v>
+        <v>11099.84415000891</v>
       </c>
       <c r="AE144" t="n">
-        <v>8340.542620233877</v>
+        <v>8295.307909465349</v>
       </c>
     </row>
     <row r="145">
@@ -9051,22 +9051,22 @@
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="n">
-        <v>17902.72667953769</v>
+        <v>21058.0196191815</v>
       </c>
       <c r="AA145" t="n">
-        <v>17458.98833898589</v>
+        <v>22261.5656158166</v>
       </c>
       <c r="AB145" t="n">
-        <v>18641.26453896059</v>
+        <v>20152.30428263895</v>
       </c>
       <c r="AC145" t="n">
-        <v>20049.07752124108</v>
+        <v>23198.00505573164</v>
       </c>
       <c r="AD145" t="n">
-        <v>18945.19526195347</v>
+        <v>17249.59132430047</v>
       </c>
       <c r="AE145" t="n">
-        <v>17969.76447200445</v>
+        <v>21159.11788811332</v>
       </c>
     </row>
     <row r="146">
@@ -9110,22 +9110,22 @@
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="n">
-        <v>3253.322979023281</v>
+        <v>4010.053599750862</v>
       </c>
       <c r="AA146" t="n">
-        <v>4317.900239001066</v>
+        <v>5167.655360015574</v>
       </c>
       <c r="AB146" t="n">
-        <v>5317.2400254288</v>
+        <v>4941.011086641981</v>
       </c>
       <c r="AC146" t="n">
-        <v>4737.262160167237</v>
+        <v>4217.747768654828</v>
       </c>
       <c r="AD146" t="n">
-        <v>3519.963209106475</v>
+        <v>4889.325019278257</v>
       </c>
       <c r="AE146" t="n">
-        <v>4264.164729014934</v>
+        <v>3083.031959348097</v>
       </c>
     </row>
     <row r="147">
@@ -9169,22 +9169,22 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="n">
-        <v>4214.49050487416</v>
+        <v>6192.25132394471</v>
       </c>
       <c r="AA147" t="n">
-        <v>5590.91767317055</v>
+        <v>5212.155665114446</v>
       </c>
       <c r="AB147" t="n">
-        <v>5077.969605051338</v>
+        <v>5008.84163697451</v>
       </c>
       <c r="AC147" t="n">
-        <v>3516.860387908689</v>
+        <v>5157.687699124131</v>
       </c>
       <c r="AD147" t="n">
-        <v>4776.215419340282</v>
+        <v>4690.564792010922</v>
       </c>
       <c r="AE147" t="n">
-        <v>5734.884852071516</v>
+        <v>6302.871341009126</v>
       </c>
     </row>
     <row r="148">
@@ -9228,22 +9228,22 @@
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="n">
-        <v>162093.3228040815</v>
+        <v>175927.8399034743</v>
       </c>
       <c r="AA148" t="n">
-        <v>197922.1312204851</v>
+        <v>176072.0099381229</v>
       </c>
       <c r="AB148" t="n">
-        <v>196900.250837621</v>
+        <v>188887.293586347</v>
       </c>
       <c r="AC148" t="n">
-        <v>149730.8288136331</v>
+        <v>165197.7620929067</v>
       </c>
       <c r="AD148" t="n">
-        <v>178287.5027615761</v>
+        <v>216636.9161928004</v>
       </c>
       <c r="AE148" t="n">
-        <v>181203.4194074449</v>
+        <v>181251.8832522345</v>
       </c>
     </row>
     <row r="149">
@@ -9287,22 +9287,22 @@
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="n">
-        <v>6014.781858368002</v>
+        <v>4870.971808645772</v>
       </c>
       <c r="AA149" t="n">
-        <v>7332.173035943595</v>
+        <v>5950.776156868817</v>
       </c>
       <c r="AB149" t="n">
-        <v>7747.368981886881</v>
+        <v>6421.445901461736</v>
       </c>
       <c r="AC149" t="n">
-        <v>5087.372941370624</v>
+        <v>5343.822586009548</v>
       </c>
       <c r="AD149" t="n">
-        <v>5743.973164578148</v>
+        <v>6141.199820977195</v>
       </c>
       <c r="AE149" t="n">
-        <v>5731.722924094229</v>
+        <v>6349.196053976048</v>
       </c>
     </row>
     <row r="150">
@@ -9346,22 +9346,22 @@
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="n">
-        <v>7733.823811067483</v>
+        <v>8632.572122827503</v>
       </c>
       <c r="AA150" t="n">
-        <v>8091.100985750079</v>
+        <v>8066.725659335121</v>
       </c>
       <c r="AB150" t="n">
-        <v>7501.576586559914</v>
+        <v>11849.51803341509</v>
       </c>
       <c r="AC150" t="n">
-        <v>6965.504550310207</v>
+        <v>6785.647745614556</v>
       </c>
       <c r="AD150" t="n">
-        <v>8439.35478764714</v>
+        <v>6914.61118516957</v>
       </c>
       <c r="AE150" t="n">
-        <v>7511.594719476077</v>
+        <v>10426.24423190599</v>
       </c>
     </row>
     <row r="151">
@@ -9405,22 +9405,22 @@
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="n">
-        <v>360959.0926155412</v>
+        <v>131556.3166614861</v>
       </c>
       <c r="AA151" t="n">
-        <v>400252.4454723662</v>
+        <v>106650.5400338524</v>
       </c>
       <c r="AB151" t="n">
-        <v>308197.78290505</v>
+        <v>157095.0577595499</v>
       </c>
       <c r="AC151" t="n">
-        <v>133082.2055163852</v>
+        <v>149986.8192896451</v>
       </c>
       <c r="AD151" t="n">
-        <v>106609.9539333435</v>
+        <v>105425.4133448579</v>
       </c>
       <c r="AE151" t="n">
-        <v>122323.8435505012</v>
+        <v>173577.5136945971</v>
       </c>
     </row>
     <row r="152">
@@ -9464,22 +9464,22 @@
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="n">
-        <v>1399780.349869754</v>
+        <v>475563.6618044755</v>
       </c>
       <c r="AA152" t="n">
-        <v>1727510.863975291</v>
+        <v>412390.4091565187</v>
       </c>
       <c r="AB152" t="n">
-        <v>1544478.797011478</v>
+        <v>361847.2678450325</v>
       </c>
       <c r="AC152" t="n">
-        <v>320926.7946565535</v>
+        <v>348614.9838688785</v>
       </c>
       <c r="AD152" t="n">
-        <v>457882.178034943</v>
+        <v>392123.6460790097</v>
       </c>
       <c r="AE152" t="n">
-        <v>338758.3691725516</v>
+        <v>384262.9358581594</v>
       </c>
     </row>
     <row r="153">
@@ -9523,22 +9523,22 @@
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="n">
-        <v>7812.349702484761</v>
+        <v>7229.606864973193</v>
       </c>
       <c r="AA153" t="n">
-        <v>7183.572366398996</v>
+        <v>6437.295508227618</v>
       </c>
       <c r="AB153" t="n">
-        <v>6789.222862389559</v>
+        <v>7893.406357946225</v>
       </c>
       <c r="AC153" t="n">
-        <v>5887.929379276481</v>
+        <v>7288.552229239736</v>
       </c>
       <c r="AD153" t="n">
-        <v>6447.710544279126</v>
+        <v>5402.007300949766</v>
       </c>
       <c r="AE153" t="n">
-        <v>5927.751164736085</v>
+        <v>6244.462459059095</v>
       </c>
     </row>
     <row r="154">
@@ -9582,22 +9582,22 @@
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="n">
-        <v>17028.82787225742</v>
+        <v>4781.677381199722</v>
       </c>
       <c r="AA154" t="n">
-        <v>11663.38088555426</v>
+        <v>6434.2532097289</v>
       </c>
       <c r="AB154" t="n">
-        <v>12419.70738693377</v>
+        <v>4619.041197205957</v>
       </c>
       <c r="AC154" t="n">
-        <v>13394.83938760894</v>
+        <v>12650.95156530326</v>
       </c>
       <c r="AD154" t="n">
-        <v>16127.69421916663</v>
+        <v>17620.98726036793</v>
       </c>
       <c r="AE154" t="n">
-        <v>13856.76816764382</v>
+        <v>14514.73024159909</v>
       </c>
     </row>
     <row r="155">
@@ -9641,22 +9641,22 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>9849.339922705894</v>
+        <v>32658.87548732051</v>
       </c>
       <c r="AA155" t="n">
-        <v>10215.38429012025</v>
+        <v>30194.94003664736</v>
       </c>
       <c r="AB155" t="n">
-        <v>9708.258115493851</v>
+        <v>28798.91591298522</v>
       </c>
       <c r="AC155" t="n">
-        <v>44809.21838471894</v>
+        <v>30059.83767546782</v>
       </c>
       <c r="AD155" t="n">
-        <v>26173.62136428782</v>
+        <v>38912.64143791518</v>
       </c>
       <c r="AE155" t="n">
-        <v>26030.76745336233</v>
+        <v>33457.80220762073</v>
       </c>
     </row>
     <row r="156">
@@ -9700,22 +9700,22 @@
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="n">
-        <v>112505.8188843994</v>
+        <v>570706.3023273221</v>
       </c>
       <c r="AA156" t="n">
-        <v>114150.0226725074</v>
+        <v>546976.5756978192</v>
       </c>
       <c r="AB156" t="n">
-        <v>111009.2522368588</v>
+        <v>488096.4552873119</v>
       </c>
       <c r="AC156" t="n">
-        <v>162585.4415245067</v>
+        <v>126139.6376474833</v>
       </c>
       <c r="AD156" t="n">
-        <v>151447.1963801617</v>
+        <v>110101.8357456689</v>
       </c>
       <c r="AE156" t="n">
-        <v>127135.2269710613</v>
+        <v>122138.87845348</v>
       </c>
     </row>
     <row r="157">
@@ -9759,22 +9759,22 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="n">
-        <v>8914.256336360882</v>
+        <v>11211.44040785451</v>
       </c>
       <c r="AA157" t="n">
-        <v>6776.166295880636</v>
+        <v>6957.54399592108</v>
       </c>
       <c r="AB157" t="n">
-        <v>9431.369425220382</v>
+        <v>8248.6576725863</v>
       </c>
       <c r="AC157" t="n">
-        <v>7718.540022819971</v>
+        <v>11847.97733933505</v>
       </c>
       <c r="AD157" t="n">
-        <v>9897.011932828536</v>
+        <v>8590.726040055204</v>
       </c>
       <c r="AE157" t="n">
-        <v>9159.989145142106</v>
+        <v>7737.673189072898</v>
       </c>
     </row>
     <row r="158">
@@ -9818,22 +9818,22 @@
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
       <c r="Z158" t="n">
-        <v>17728.3120622385</v>
+        <v>17415.73391016894</v>
       </c>
       <c r="AA158" t="n">
-        <v>22181.07322852364</v>
+        <v>18822.5524650444</v>
       </c>
       <c r="AB158" t="n">
-        <v>17325.14052585516</v>
+        <v>17970.89064145388</v>
       </c>
       <c r="AC158" t="n">
-        <v>16320.62069394142</v>
+        <v>14018.38281815708</v>
       </c>
       <c r="AD158" t="n">
-        <v>19903.69621515958</v>
+        <v>15458.48659597186</v>
       </c>
       <c r="AE158" t="n">
-        <v>13584.1290538704</v>
+        <v>21478.32018021792</v>
       </c>
     </row>
     <row r="159">
@@ -9877,22 +9877,22 @@
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="n">
-        <v>38565.69721450655</v>
+        <v>49087.81740929529</v>
       </c>
       <c r="AA159" t="n">
-        <v>62111.52740561869</v>
+        <v>50274.21576586754</v>
       </c>
       <c r="AB159" t="n">
-        <v>45932.04100781064</v>
+        <v>48023.0008427331</v>
       </c>
       <c r="AC159" t="n">
-        <v>40334.27878084769</v>
+        <v>59762.86503649515</v>
       </c>
       <c r="AD159" t="n">
-        <v>38182.18634152434</v>
+        <v>43611.00765141065</v>
       </c>
       <c r="AE159" t="n">
-        <v>48103.33953780436</v>
+        <v>47108.37570351476</v>
       </c>
     </row>
     <row r="160">
@@ -9936,22 +9936,22 @@
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="n">
-        <v>33676.95437827693</v>
+        <v>112736.4699979989</v>
       </c>
       <c r="AA160" t="n">
-        <v>41716.38117209081</v>
+        <v>84205.46805115303</v>
       </c>
       <c r="AB160" t="n">
-        <v>33484.52882011142</v>
+        <v>100897.4259906664</v>
       </c>
       <c r="AC160" t="n">
-        <v>25553.93287820286</v>
+        <v>34795.46831899966</v>
       </c>
       <c r="AD160" t="n">
-        <v>38527.75752317817</v>
+        <v>38213.35267740451</v>
       </c>
       <c r="AE160" t="n">
-        <v>32918.02651785136</v>
+        <v>48035.9245663252</v>
       </c>
     </row>
     <row r="161">
@@ -9995,22 +9995,22 @@
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
       <c r="Z161" t="n">
-        <v>15727.23655300667</v>
+        <v>13319.63809732529</v>
       </c>
       <c r="AA161" t="n">
-        <v>15711.1501719653</v>
+        <v>15528.82643949032</v>
       </c>
       <c r="AB161" t="n">
-        <v>15635.70299102765</v>
+        <v>16116.33790890843</v>
       </c>
       <c r="AC161" t="n">
-        <v>14858.27013719299</v>
+        <v>16083.02611843764</v>
       </c>
       <c r="AD161" t="n">
-        <v>16067.79427365202</v>
+        <v>15033.90389931048</v>
       </c>
       <c r="AE161" t="n">
-        <v>15915.8417965994</v>
+        <v>15328.28837024788</v>
       </c>
     </row>
     <row r="162">
@@ -10054,22 +10054,22 @@
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="n">
-        <v>5403.690089276919</v>
+        <v>44582.86404270639</v>
       </c>
       <c r="AA162" t="n">
-        <v>7573.308727540136</v>
+        <v>50869.6684154156</v>
       </c>
       <c r="AB162" t="n">
-        <v>6783.942468505802</v>
+        <v>31716.71963465759</v>
       </c>
       <c r="AC162" t="n">
-        <v>16589.06857749313</v>
+        <v>19612.63386461266</v>
       </c>
       <c r="AD162" t="n">
-        <v>15144.4036766494</v>
+        <v>25012.33148839422</v>
       </c>
       <c r="AE162" t="n">
-        <v>19230.18041066028</v>
+        <v>25184.26804482561</v>
       </c>
     </row>
     <row r="163">
@@ -10113,22 +10113,22 @@
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="n">
-        <v>2737.290046959178</v>
+        <v>2428.949859947572</v>
       </c>
       <c r="AA163" t="n">
-        <v>2665.255339414945</v>
+        <v>2322.791462750398</v>
       </c>
       <c r="AB163" t="n">
-        <v>2289.961611298759</v>
+        <v>2694.800929506564</v>
       </c>
       <c r="AC163" t="n">
-        <v>5499.302867815794</v>
+        <v>5953.968281837932</v>
       </c>
       <c r="AD163" t="n">
-        <v>5549.480418470422</v>
+        <v>5181.082653203017</v>
       </c>
       <c r="AE163" t="n">
-        <v>4478.593385424141</v>
+        <v>5876.414670687972</v>
       </c>
     </row>
     <row r="164">
@@ -10172,22 +10172,22 @@
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="n">
-        <v>13955.13588421201</v>
+        <v>18195.18882318957</v>
       </c>
       <c r="AA164" t="n">
-        <v>17894.44927839443</v>
+        <v>13467.4623462045</v>
       </c>
       <c r="AB164" t="n">
-        <v>14847.51976563067</v>
+        <v>14980.78026829445</v>
       </c>
       <c r="AC164" t="n">
-        <v>13654.10350714162</v>
+        <v>16962.72367286559</v>
       </c>
       <c r="AD164" t="n">
-        <v>18333.88799534377</v>
+        <v>20165.46377188103</v>
       </c>
       <c r="AE164" t="n">
-        <v>14363.82053516184</v>
+        <v>20055.73330058751</v>
       </c>
     </row>
     <row r="165">
@@ -10231,22 +10231,22 @@
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr"/>
       <c r="Z165" t="n">
-        <v>20620.48802801513</v>
+        <v>31220.82397962482</v>
       </c>
       <c r="AA165" t="n">
-        <v>14322.56872151089</v>
+        <v>35284.93860034184</v>
       </c>
       <c r="AB165" t="n">
-        <v>19916.71070596623</v>
+        <v>28495.48797237683</v>
       </c>
       <c r="AC165" t="n">
-        <v>15052.75547178151</v>
+        <v>20988.29199554661</v>
       </c>
       <c r="AD165" t="n">
-        <v>18343.37588402454</v>
+        <v>17123.79887414808</v>
       </c>
       <c r="AE165" t="n">
-        <v>16950.04972324021</v>
+        <v>15137.35565557405</v>
       </c>
     </row>
     <row r="166">
@@ -10290,22 +10290,22 @@
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="n">
-        <v>118096.9366167062</v>
+        <v>21888.89622705266</v>
       </c>
       <c r="AA166" t="n">
-        <v>103945.0071504259</v>
+        <v>24265.39221214881</v>
       </c>
       <c r="AB166" t="n">
-        <v>92062.04531927263</v>
+        <v>27540.36988574673</v>
       </c>
       <c r="AC166" t="n">
-        <v>28409.07609549983</v>
+        <v>25944.09262038527</v>
       </c>
       <c r="AD166" t="n">
-        <v>28531.35950004358</v>
+        <v>31305.10903263985</v>
       </c>
       <c r="AE166" t="n">
-        <v>32418.58108216624</v>
+        <v>24443.16745699747</v>
       </c>
     </row>
     <row r="167">
@@ -10349,22 +10349,22 @@
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="n">
-        <v>12170.80318630964</v>
+        <v>4438.418820937785</v>
       </c>
       <c r="AA167" t="n">
-        <v>12755.66378579722</v>
+        <v>5753.995978399566</v>
       </c>
       <c r="AB167" t="n">
-        <v>10220.45585828137</v>
+        <v>6133.974187024451</v>
       </c>
       <c r="AC167" t="n">
-        <v>13354.44037451732</v>
+        <v>14980.54992494496</v>
       </c>
       <c r="AD167" t="n">
-        <v>13205.08806413306</v>
+        <v>11820.60096324182</v>
       </c>
       <c r="AE167" t="n">
-        <v>9068.3415426509</v>
+        <v>13543.04857581968</v>
       </c>
     </row>
     <row r="168">
@@ -10408,22 +10408,22 @@
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="n">
-        <v>9851.868655762335</v>
+        <v>29849.72498652897</v>
       </c>
       <c r="AA168" t="n">
-        <v>7673.287796910819</v>
+        <v>34867.14835813752</v>
       </c>
       <c r="AB168" t="n">
-        <v>9971.339262275751</v>
+        <v>31809.25607192246</v>
       </c>
       <c r="AC168" t="n">
-        <v>37577.44627733019</v>
+        <v>32044.58375657471</v>
       </c>
       <c r="AD168" t="n">
-        <v>44027.96289497045</v>
+        <v>35035.06502879596</v>
       </c>
       <c r="AE168" t="n">
-        <v>37175.21331771449</v>
+        <v>40938.30715370398</v>
       </c>
     </row>
     <row r="169">
@@ -10467,22 +10467,22 @@
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="n">
-        <v>42244.41872812983</v>
+        <v>56608.50540524007</v>
       </c>
       <c r="AA169" t="n">
-        <v>60176.44351904704</v>
+        <v>46951.38508210264</v>
       </c>
       <c r="AB169" t="n">
-        <v>65005.11829155629</v>
+        <v>68690.8029401063</v>
       </c>
       <c r="AC169" t="n">
-        <v>49743.86757656131</v>
+        <v>60094.76674007236</v>
       </c>
       <c r="AD169" t="n">
-        <v>72883.74411468556</v>
+        <v>59598.81593090624</v>
       </c>
       <c r="AE169" t="n">
-        <v>72486.75384856011</v>
+        <v>61007.63462555798</v>
       </c>
     </row>
     <row r="170">
@@ -10526,22 +10526,22 @@
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="n">
-        <v>21633.04268289857</v>
+        <v>7442.527081112273</v>
       </c>
       <c r="AA170" t="n">
-        <v>25424.53401927343</v>
+        <v>6103.36610645271</v>
       </c>
       <c r="AB170" t="n">
-        <v>20451.71536904383</v>
+        <v>6358.947750660302</v>
       </c>
       <c r="AC170" t="n">
-        <v>29249.92203507125</v>
+        <v>21908.60902723343</v>
       </c>
       <c r="AD170" t="n">
-        <v>16736.89904418357</v>
+        <v>22697.74275550224</v>
       </c>
       <c r="AE170" t="n">
-        <v>25146.53634687639</v>
+        <v>21215.1393781175</v>
       </c>
     </row>
     <row r="171">
@@ -10585,22 +10585,22 @@
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr"/>
       <c r="Z171" t="n">
-        <v>60661.49180342082</v>
+        <v>41870.67929394137</v>
       </c>
       <c r="AA171" t="n">
-        <v>83014.06969650215</v>
+        <v>33660.03251501143</v>
       </c>
       <c r="AB171" t="n">
-        <v>65614.59724461683</v>
+        <v>29457.82463804459</v>
       </c>
       <c r="AC171" t="n">
-        <v>27770.36305646965</v>
+        <v>33523.76825718451</v>
       </c>
       <c r="AD171" t="n">
-        <v>29855.98571469805</v>
+        <v>34581.30989270363</v>
       </c>
       <c r="AE171" t="n">
-        <v>34005.81378997007</v>
+        <v>25532.76104570513</v>
       </c>
     </row>
     <row r="172">
@@ -10644,22 +10644,22 @@
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr"/>
       <c r="Z172" t="n">
-        <v>6124.085089748179</v>
+        <v>69139.49357605727</v>
       </c>
       <c r="AA172" t="n">
-        <v>8225.024905426408</v>
+        <v>54153.32093138297</v>
       </c>
       <c r="AB172" t="n">
-        <v>8031.624322428316</v>
+        <v>53650.77873797742</v>
       </c>
       <c r="AC172" t="n">
-        <v>25542.11748613341</v>
+        <v>28851.70131102233</v>
       </c>
       <c r="AD172" t="n">
-        <v>22662.29237580964</v>
+        <v>25608.83526373787</v>
       </c>
       <c r="AE172" t="n">
-        <v>20903.98282199348</v>
+        <v>18752.54747025372</v>
       </c>
     </row>
     <row r="173">
@@ -10703,22 +10703,22 @@
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr"/>
       <c r="Z173" t="n">
-        <v>24519.9871376908</v>
+        <v>19068.07454297279</v>
       </c>
       <c r="AA173" t="n">
-        <v>22066.17581453175</v>
+        <v>14993.51033027522</v>
       </c>
       <c r="AB173" t="n">
-        <v>23300.78571938766</v>
+        <v>21874.92543513612</v>
       </c>
       <c r="AC173" t="n">
-        <v>21993.19995482079</v>
+        <v>21774.19791953002</v>
       </c>
       <c r="AD173" t="n">
-        <v>16937.23289028402</v>
+        <v>24079.5352100259</v>
       </c>
       <c r="AE173" t="n">
-        <v>21637.4191562934</v>
+        <v>16897.83989960499</v>
       </c>
     </row>
     <row r="174">
@@ -10762,22 +10762,22 @@
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>14444.02980770918</v>
+        <v>11277.8762805412</v>
       </c>
       <c r="AA174" t="n">
-        <v>11111.76863382443</v>
+        <v>12042.15358373197</v>
       </c>
       <c r="AB174" t="n">
-        <v>11769.17599663314</v>
+        <v>11162.01314667675</v>
       </c>
       <c r="AC174" t="n">
-        <v>8707.881739553864</v>
+        <v>10393.22168571054</v>
       </c>
       <c r="AD174" t="n">
-        <v>10857.04465450016</v>
+        <v>13480.32932148086</v>
       </c>
       <c r="AE174" t="n">
-        <v>8394.272765928925</v>
+        <v>10881.99394230074</v>
       </c>
     </row>
     <row r="175">
@@ -10821,22 +10821,22 @@
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>25336.51852023838</v>
+        <v>28436.60566968761</v>
       </c>
       <c r="AA175" t="n">
-        <v>30428.23132280396</v>
+        <v>31487.61978823677</v>
       </c>
       <c r="AB175" t="n">
-        <v>24485.92880279389</v>
+        <v>25985.92486905004</v>
       </c>
       <c r="AC175" t="n">
-        <v>28826.91003224814</v>
+        <v>25573.23861816548</v>
       </c>
       <c r="AD175" t="n">
-        <v>36454.05310440335</v>
+        <v>37567.55214218109</v>
       </c>
       <c r="AE175" t="n">
-        <v>21265.53073259703</v>
+        <v>35783.81051766701</v>
       </c>
     </row>
     <row r="176">
@@ -10880,22 +10880,22 @@
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>17625.35714416219</v>
+        <v>19150.01591885975</v>
       </c>
       <c r="AA176" t="n">
-        <v>19385.41588564039</v>
+        <v>17955.14851218013</v>
       </c>
       <c r="AB176" t="n">
-        <v>21001.92595904967</v>
+        <v>22278.01960018877</v>
       </c>
       <c r="AC176" t="n">
-        <v>21110.33400619612</v>
+        <v>19308.86321767419</v>
       </c>
       <c r="AD176" t="n">
-        <v>16978.9262659986</v>
+        <v>18891.58186975069</v>
       </c>
       <c r="AE176" t="n">
-        <v>23020.22075122017</v>
+        <v>19944.34719504265</v>
       </c>
     </row>
     <row r="177">
@@ -10939,22 +10939,22 @@
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>538299.1797195149</v>
+        <v>183683.0792794971</v>
       </c>
       <c r="AA177" t="n">
-        <v>441745.1653713368</v>
+        <v>146626.4943093351</v>
       </c>
       <c r="AB177" t="n">
-        <v>496559.9803650756</v>
+        <v>180343.5035220972</v>
       </c>
       <c r="AC177" t="n">
-        <v>195851.7189649377</v>
+        <v>140680.8558131272</v>
       </c>
       <c r="AD177" t="n">
-        <v>187893.0974948652</v>
+        <v>188928.9234097131</v>
       </c>
       <c r="AE177" t="n">
-        <v>154109.5619649091</v>
+        <v>127275.0912001278</v>
       </c>
     </row>
     <row r="178">
@@ -10998,22 +10998,22 @@
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>35040.2314941802</v>
+        <v>116568.0579725286</v>
       </c>
       <c r="AA178" t="n">
-        <v>26901.22080596684</v>
+        <v>120418.2148955856</v>
       </c>
       <c r="AB178" t="n">
-        <v>25595.35594247148</v>
+        <v>79982.48598320478</v>
       </c>
       <c r="AC178" t="n">
-        <v>104006.2963230343</v>
+        <v>92635.08202678237</v>
       </c>
       <c r="AD178" t="n">
-        <v>92594.16270281935</v>
+        <v>96743.14920037784</v>
       </c>
       <c r="AE178" t="n">
-        <v>99213.13816915581</v>
+        <v>103232.6887600264</v>
       </c>
     </row>
     <row r="179">
@@ -11057,22 +11057,22 @@
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>26970.26941928641</v>
+        <v>30790.38607993484</v>
       </c>
       <c r="AA179" t="n">
-        <v>28967.55860674048</v>
+        <v>34140.8244770308</v>
       </c>
       <c r="AB179" t="n">
-        <v>36917.09101622831</v>
+        <v>24150.43898859172</v>
       </c>
       <c r="AC179" t="n">
-        <v>40766.39569722103</v>
+        <v>33518.89066982888</v>
       </c>
       <c r="AD179" t="n">
-        <v>29291.70792575673</v>
+        <v>32511.52269598682</v>
       </c>
       <c r="AE179" t="n">
-        <v>26314.62677116231</v>
+        <v>31616.25617012092</v>
       </c>
     </row>
     <row r="180">
@@ -11116,22 +11116,22 @@
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="n">
-        <v>10660.4744970892</v>
+        <v>4546.549961788549</v>
       </c>
       <c r="AA180" t="n">
-        <v>8513.389679427994</v>
+        <v>5541.03500702205</v>
       </c>
       <c r="AB180" t="n">
-        <v>12820.9261045033</v>
+        <v>3868.794931494475</v>
       </c>
       <c r="AC180" t="n">
-        <v>11945.01608028986</v>
+        <v>12516.39632763856</v>
       </c>
       <c r="AD180" t="n">
-        <v>12817.30942791564</v>
+        <v>9386.055157770475</v>
       </c>
       <c r="AE180" t="n">
-        <v>8311.931859031845</v>
+        <v>14063.56378246889</v>
       </c>
     </row>
     <row r="181">
@@ -11175,22 +11175,22 @@
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="n">
-        <v>26196.27454901825</v>
+        <v>12865.19144085796</v>
       </c>
       <c r="AA181" t="n">
-        <v>21522.64533937909</v>
+        <v>16262.21551062595</v>
       </c>
       <c r="AB181" t="n">
-        <v>26090.67285126754</v>
+        <v>14771.07627126946</v>
       </c>
       <c r="AC181" t="n">
-        <v>6968.04802379068</v>
+        <v>11036.57633553777</v>
       </c>
       <c r="AD181" t="n">
-        <v>6675.536502866361</v>
+        <v>9233.551897042407</v>
       </c>
       <c r="AE181" t="n">
-        <v>7055.148218044611</v>
+        <v>5819.780592191249</v>
       </c>
     </row>
     <row r="182">
@@ -11234,22 +11234,22 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="n">
-        <v>224800.0849617728</v>
+        <v>72554.53844414251</v>
       </c>
       <c r="AA182" t="n">
-        <v>305413.0330385141</v>
+        <v>76826.00159552527</v>
       </c>
       <c r="AB182" t="n">
-        <v>350793.0852451996</v>
+        <v>71369.78903684078</v>
       </c>
       <c r="AC182" t="n">
-        <v>81118.08608414479</v>
+        <v>66380.27249406141</v>
       </c>
       <c r="AD182" t="n">
-        <v>77689.4560550579</v>
+        <v>76549.86791725943</v>
       </c>
       <c r="AE182" t="n">
-        <v>64971.65481307745</v>
+        <v>68359.87527520601</v>
       </c>
     </row>
     <row r="183">
@@ -11293,22 +11293,22 @@
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>91530.93835142291</v>
+        <v>42293.9904049551</v>
       </c>
       <c r="AA183" t="n">
-        <v>84845.44383269994</v>
+        <v>27937.07770762244</v>
       </c>
       <c r="AB183" t="n">
-        <v>109112.2635437101</v>
+        <v>28525.4473307698</v>
       </c>
       <c r="AC183" t="n">
-        <v>38285.18355320717</v>
+        <v>35526.85785256253</v>
       </c>
       <c r="AD183" t="n">
-        <v>21634.97522964844</v>
+        <v>27723.75361495696</v>
       </c>
       <c r="AE183" t="n">
-        <v>30316.42351488387</v>
+        <v>36998.29565654613</v>
       </c>
     </row>
     <row r="184">
@@ -11352,22 +11352,22 @@
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>33409.72861406718</v>
+        <v>36812.96473834416</v>
       </c>
       <c r="AA184" t="n">
-        <v>34952.34033403689</v>
+        <v>40241.7294999775</v>
       </c>
       <c r="AB184" t="n">
-        <v>37535.83770941451</v>
+        <v>36826.6622438975</v>
       </c>
       <c r="AC184" t="n">
-        <v>47773.00898972684</v>
+        <v>36927.29562668696</v>
       </c>
       <c r="AD184" t="n">
-        <v>47074.70267879265</v>
+        <v>42581.96940131098</v>
       </c>
       <c r="AE184" t="n">
-        <v>38102.08051201798</v>
+        <v>38087.45167840529</v>
       </c>
     </row>
     <row r="185">
@@ -11411,22 +11411,22 @@
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="n">
-        <v>3559.323405318199</v>
+        <v>16250.36838723233</v>
       </c>
       <c r="AA185" t="n">
-        <v>4468.326447229669</v>
+        <v>14395.219649719</v>
       </c>
       <c r="AB185" t="n">
-        <v>4317.524323881766</v>
+        <v>15108.85270656608</v>
       </c>
       <c r="AC185" t="n">
-        <v>3200.985566507698</v>
+        <v>3762.078461665321</v>
       </c>
       <c r="AD185" t="n">
-        <v>4212.501286123482</v>
+        <v>2778.931281220734</v>
       </c>
       <c r="AE185" t="n">
-        <v>4038.148040242373</v>
+        <v>4187.71690940747</v>
       </c>
     </row>
     <row r="186">
@@ -11470,22 +11470,22 @@
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="n">
-        <v>62901.71291817955</v>
+        <v>22088.88884024557</v>
       </c>
       <c r="AA186" t="n">
-        <v>65272.2355856099</v>
+        <v>26287.81277616315</v>
       </c>
       <c r="AB186" t="n">
-        <v>56704.85850439808</v>
+        <v>18442.92730004691</v>
       </c>
       <c r="AC186" t="n">
-        <v>48458.28069461307</v>
+        <v>59416.52404952801</v>
       </c>
       <c r="AD186" t="n">
-        <v>54179.80438463098</v>
+        <v>41164.15335151531</v>
       </c>
       <c r="AE186" t="n">
-        <v>57712.47307032665</v>
+        <v>56648.80360177391</v>
       </c>
     </row>
     <row r="187">
@@ -11529,22 +11529,22 @@
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="n">
-        <v>35978.22942037967</v>
+        <v>16867.82138559725</v>
       </c>
       <c r="AA187" t="n">
-        <v>40469.17550407362</v>
+        <v>14297.61506640275</v>
       </c>
       <c r="AB187" t="n">
-        <v>35384.7058064834</v>
+        <v>12968.1382293802</v>
       </c>
       <c r="AC187" t="n">
-        <v>43354.16934407091</v>
+        <v>35021.16285583266</v>
       </c>
       <c r="AD187" t="n">
-        <v>37826.01281794547</v>
+        <v>39096.8091996849</v>
       </c>
       <c r="AE187" t="n">
-        <v>43962.20510809651</v>
+        <v>36457.84238949314</v>
       </c>
     </row>
     <row r="188">
@@ -11588,22 +11588,22 @@
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="n">
-        <v>5559.842206072989</v>
+        <v>2478.000980543168</v>
       </c>
       <c r="AA188" t="n">
-        <v>7298.369869270831</v>
+        <v>2341.18810366415</v>
       </c>
       <c r="AB188" t="n">
-        <v>8210.197723157969</v>
+        <v>2121.176906836085</v>
       </c>
       <c r="AC188" t="n">
-        <v>6190.84680213752</v>
+        <v>7377.046796465525</v>
       </c>
       <c r="AD188" t="n">
-        <v>5872.856381774488</v>
+        <v>7322.005777960489</v>
       </c>
       <c r="AE188" t="n">
-        <v>6182.204797824254</v>
+        <v>8153.566722205951</v>
       </c>
     </row>
     <row r="189">
@@ -11647,22 +11647,22 @@
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr"/>
       <c r="Z189" t="n">
-        <v>14850.46939742025</v>
+        <v>13398.71459210393</v>
       </c>
       <c r="AA189" t="n">
-        <v>12109.17118130313</v>
+        <v>12792.44085061028</v>
       </c>
       <c r="AB189" t="n">
-        <v>13623.92606688935</v>
+        <v>14354.41289351401</v>
       </c>
       <c r="AC189" t="n">
-        <v>11272.19127594044</v>
+        <v>12928.96236207437</v>
       </c>
       <c r="AD189" t="n">
-        <v>16413.42380687423</v>
+        <v>14271.8185008386</v>
       </c>
       <c r="AE189" t="n">
-        <v>13632.81403942499</v>
+        <v>12173.93225994089</v>
       </c>
     </row>
     <row r="190">
@@ -11706,22 +11706,22 @@
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr"/>
       <c r="Z190" t="n">
-        <v>26293.74537004809</v>
+        <v>25509.21006222005</v>
       </c>
       <c r="AA190" t="n">
-        <v>24371.32170949004</v>
+        <v>32284.33679132137</v>
       </c>
       <c r="AB190" t="n">
-        <v>25702.00192850809</v>
+        <v>34560.24497028687</v>
       </c>
       <c r="AC190" t="n">
-        <v>26656.49420109261</v>
+        <v>23248.6130480003</v>
       </c>
       <c r="AD190" t="n">
-        <v>27313.03905012097</v>
+        <v>23500.04908512369</v>
       </c>
       <c r="AE190" t="n">
-        <v>33983.16987729027</v>
+        <v>32709.66867097712</v>
       </c>
     </row>
     <row r="191">
@@ -11765,22 +11765,22 @@
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr"/>
       <c r="Z191" t="n">
-        <v>28103.06378568662</v>
+        <v>24760.67534814745</v>
       </c>
       <c r="AA191" t="n">
-        <v>24444.42699284113</v>
+        <v>29063.05225293661</v>
       </c>
       <c r="AB191" t="n">
-        <v>21813.75119076432</v>
+        <v>21758.63311564671</v>
       </c>
       <c r="AC191" t="n">
-        <v>24723.28533834223</v>
+        <v>18415.0403122979</v>
       </c>
       <c r="AD191" t="n">
-        <v>22513.18397649255</v>
+        <v>23132.2202743756</v>
       </c>
       <c r="AE191" t="n">
-        <v>28061.33052732393</v>
+        <v>18892.42535452987</v>
       </c>
     </row>
     <row r="192">
@@ -11824,22 +11824,22 @@
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr"/>
       <c r="Z192" t="n">
-        <v>14968.31157379267</v>
+        <v>14473.84108203357</v>
       </c>
       <c r="AA192" t="n">
-        <v>17408.6209491346</v>
+        <v>15352.02613736281</v>
       </c>
       <c r="AB192" t="n">
-        <v>18086.39669464572</v>
+        <v>11300.17891287068</v>
       </c>
       <c r="AC192" t="n">
-        <v>16195.18586459303</v>
+        <v>18138.92656133549</v>
       </c>
       <c r="AD192" t="n">
-        <v>15276.64502142601</v>
+        <v>22211.27286643504</v>
       </c>
       <c r="AE192" t="n">
-        <v>13287.30393301735</v>
+        <v>17276.18098502512</v>
       </c>
     </row>
     <row r="193">
@@ -11883,22 +11883,22 @@
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr"/>
       <c r="Z193" t="n">
-        <v>57342.9071379615</v>
+        <v>21946.2051484428</v>
       </c>
       <c r="AA193" t="n">
-        <v>76526.80857832376</v>
+        <v>18634.97877198383</v>
       </c>
       <c r="AB193" t="n">
-        <v>63117.01883561065</v>
+        <v>15381.37748652877</v>
       </c>
       <c r="AC193" t="n">
-        <v>18014.40849963429</v>
+        <v>19053.51196003734</v>
       </c>
       <c r="AD193" t="n">
-        <v>18204.31661374204</v>
+        <v>22474.61378311032</v>
       </c>
       <c r="AE193" t="n">
-        <v>18951.88003132076</v>
+        <v>20400.66702143608</v>
       </c>
     </row>
     <row r="194">
@@ -11942,22 +11942,22 @@
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr"/>
       <c r="Z194" t="n">
-        <v>18567.95201031442</v>
+        <v>50015.45130983549</v>
       </c>
       <c r="AA194" t="n">
-        <v>20191.55182341232</v>
+        <v>44551.70909921422</v>
       </c>
       <c r="AB194" t="n">
-        <v>18016.69520372219</v>
+        <v>37509.09454601105</v>
       </c>
       <c r="AC194" t="n">
-        <v>15473.6019739942</v>
+        <v>15655.99652074838</v>
       </c>
       <c r="AD194" t="n">
-        <v>19000.5501603522</v>
+        <v>17561.75145809313</v>
       </c>
       <c r="AE194" t="n">
-        <v>20988.72748536999</v>
+        <v>15608.62084023445</v>
       </c>
     </row>
     <row r="195">
@@ -12001,22 +12001,22 @@
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr"/>
       <c r="Z195" t="n">
-        <v>28767.49792170341</v>
+        <v>27106.86303115814</v>
       </c>
       <c r="AA195" t="n">
-        <v>25152.89337450788</v>
+        <v>24728.1682322923</v>
       </c>
       <c r="AB195" t="n">
-        <v>28369.62752221547</v>
+        <v>23597.6681511711</v>
       </c>
       <c r="AC195" t="n">
-        <v>23056.70631296284</v>
+        <v>25689.51872822823</v>
       </c>
       <c r="AD195" t="n">
-        <v>26660.77170847367</v>
+        <v>24021.49721212523</v>
       </c>
       <c r="AE195" t="n">
-        <v>27688.55355973272</v>
+        <v>25569.60756790664</v>
       </c>
     </row>
     <row r="196">
@@ -12060,22 +12060,22 @@
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr"/>
       <c r="Z196" t="n">
-        <v>102611.662780544</v>
+        <v>91909.03923373054</v>
       </c>
       <c r="AA196" t="n">
-        <v>79607.30119361669</v>
+        <v>110669.1081921198</v>
       </c>
       <c r="AB196" t="n">
-        <v>90695.74785287106</v>
+        <v>90240.50644391822</v>
       </c>
       <c r="AC196" t="n">
-        <v>84083.49133838917</v>
+        <v>108091.3315170552</v>
       </c>
       <c r="AD196" t="n">
-        <v>105794.5404162218</v>
+        <v>90427.71174104736</v>
       </c>
       <c r="AE196" t="n">
-        <v>98792.94039736989</v>
+        <v>87387.79880223739</v>
       </c>
     </row>
     <row r="197">
@@ -12119,22 +12119,22 @@
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>1313.567453024451</v>
+        <v>1810.64134538485</v>
       </c>
       <c r="AA197" t="n">
-        <v>1612.394418322751</v>
+        <v>1206.615926584629</v>
       </c>
       <c r="AB197" t="n">
-        <v>1894.629878402971</v>
+        <v>1701.267307840258</v>
       </c>
       <c r="AC197" t="n">
-        <v>2381.739758671418</v>
+        <v>1737.836365787586</v>
       </c>
       <c r="AD197" t="n">
-        <v>1689.220325566688</v>
+        <v>1229.007086585187</v>
       </c>
       <c r="AE197" t="n">
-        <v>1637.111774381843</v>
+        <v>1440.270698596397</v>
       </c>
     </row>
     <row r="198">
@@ -12178,22 +12178,22 @@
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="n">
-        <v>65182.2064043725</v>
+        <v>5739.858311099899</v>
       </c>
       <c r="AA198" t="n">
-        <v>62119.8781660224</v>
+        <v>5310.732254827732</v>
       </c>
       <c r="AB198" t="n">
-        <v>63644.17141019639</v>
+        <v>5737.212896208044</v>
       </c>
       <c r="AC198" t="n">
-        <v>18174.52916030372</v>
+        <v>15752.29731668977</v>
       </c>
       <c r="AD198" t="n">
-        <v>18772.1507442252</v>
+        <v>18066.15899809692</v>
       </c>
       <c r="AE198" t="n">
-        <v>16408.90733632504</v>
+        <v>16483.37414390052</v>
       </c>
     </row>
     <row r="199">
@@ -12237,22 +12237,22 @@
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr"/>
       <c r="Z199" t="n">
-        <v>22502.15167502324</v>
+        <v>30237.69156345246</v>
       </c>
       <c r="AA199" t="n">
-        <v>25494.03888401815</v>
+        <v>23368.63391725671</v>
       </c>
       <c r="AB199" t="n">
-        <v>21835.45837421593</v>
+        <v>30758.24486400055</v>
       </c>
       <c r="AC199" t="n">
-        <v>30017.21350318926</v>
+        <v>31585.59258396687</v>
       </c>
       <c r="AD199" t="n">
-        <v>24678.43612149521</v>
+        <v>29831.93931539171</v>
       </c>
       <c r="AE199" t="n">
-        <v>27439.67618236571</v>
+        <v>22268.18208090957</v>
       </c>
     </row>
     <row r="200">
@@ -12296,22 +12296,22 @@
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="n">
-        <v>30677.5196512347</v>
+        <v>22500.28100115688</v>
       </c>
       <c r="AA200" t="n">
-        <v>27154.82085923255</v>
+        <v>20909.11752057236</v>
       </c>
       <c r="AB200" t="n">
-        <v>36766.40164582456</v>
+        <v>26758.07012749387</v>
       </c>
       <c r="AC200" t="n">
-        <v>27519.01142840905</v>
+        <v>37529.09640126609</v>
       </c>
       <c r="AD200" t="n">
-        <v>41375.89591164272</v>
+        <v>23380.34732616763</v>
       </c>
       <c r="AE200" t="n">
-        <v>28513.64064675293</v>
+        <v>31082.91559053624</v>
       </c>
     </row>
     <row r="201">
@@ -12355,22 +12355,22 @@
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="n">
-        <v>12265.24894126068</v>
+        <v>4473.265298673517</v>
       </c>
       <c r="AA201" t="n">
-        <v>15772.4202651547</v>
+        <v>4071.103009250572</v>
       </c>
       <c r="AB201" t="n">
-        <v>14086.52163973165</v>
+        <v>4133.448494452681</v>
       </c>
       <c r="AC201" t="n">
-        <v>14767.61545157622</v>
+        <v>16354.67252718961</v>
       </c>
       <c r="AD201" t="n">
-        <v>12002.80745768587</v>
+        <v>13751.08329156833</v>
       </c>
       <c r="AE201" t="n">
-        <v>15088.6581627038</v>
+        <v>12779.18040174102</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/sample_dataset.xlsx
+++ b/sample_data/sample_dataset.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Gene</t>
+          <t>Gene Symbol</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -756,11 +756,7 @@
           <t>P00003</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GENE3</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Example protein</t>
@@ -1582,11 +1578,7 @@
           <t>P00017</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GENE17</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Example protein</t>
@@ -3057,11 +3049,7 @@
           <t>P00042</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GENE42</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Example protein</t>
